--- a/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
+++ b/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Items'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Items'!$A$1:$G$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -666,7 +666,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-09-28   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
+          <t>As of 2026-10-01   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
         </is>
       </c>
     </row>
@@ -706,8 +706,8 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTA('CNG Feature Matrix'!A2:A103)</f>
-        <v>102</v>
+        <f>COUNTA('CNG Feature Matrix'!A2:A104)</f>
+        <v>103</v>
       </c>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="9" t="inlineStr">
@@ -723,12 +723,12 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E103,"Yes")</f>
-        <v>68</v>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>73</v>
       </c>
       <c r="C8" s="12">
         <f>B8/$B$7</f>
-        <v>0.6666666667</v>
+        <v>0.7087378640776699</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -743,12 +743,12 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E103,"Partial")</f>
-        <v>14</v>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <v>10</v>
       </c>
       <c r="C9" s="12">
         <f>B9/$B$7</f>
-        <v>0.137254902</v>
+        <v>0.0970873786407767</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -763,12 +763,12 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"No")</f>
         <v>20</v>
       </c>
       <c r="C10" s="12">
         <f>B10/$B$7</f>
-        <v>0.1960784314</v>
+        <v>0.1941747572815534</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
@@ -819,12 +819,12 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H103,A15)</f>
-        <v>16</v>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A15)</f>
+        <v>12</v>
       </c>
       <c r="C15" s="12">
-        <f>IFERROR(B15/(COUNTIF('CNG Feature Matrix'!E2:E103,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E103,"No")),0)</f>
-        <v>0.4705882353</v>
+        <f>IFERROR(B15/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <v>0.4</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
@@ -839,12 +839,12 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H103,A16)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A16)</f>
         <v>6</v>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR(B16/(COUNTIF('CNG Feature Matrix'!E2:E103,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E103,"No")),0)</f>
-        <v>0.1764705882</v>
+        <f>IFERROR(B16/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <v>0.2</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
@@ -859,12 +859,12 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H103,A17)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A17)</f>
         <v>5</v>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR(B17/(COUNTIF('CNG Feature Matrix'!E2:E103,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E103,"No")),0)</f>
-        <v>0.1470588235</v>
+        <f>IFERROR(B17/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <v>0.16666666666666666</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -879,12 +879,12 @@
         </is>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H103,A18)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A18)</f>
         <v>4</v>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(B18/(COUNTIF('CNG Feature Matrix'!E2:E103,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E103,"No")),0)</f>
-        <v>0.1176470588</v>
+        <f>IFERROR(B18/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <v>0.13333333333333333</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
@@ -899,12 +899,12 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H103,A19)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A19)</f>
         <v>3</v>
       </c>
       <c r="C19" s="12">
-        <f>IFERROR(B19/(COUNTIF('CNG Feature Matrix'!E2:E103,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E103,"No")),0)</f>
-        <v>0.0882352941</v>
+        <f>IFERROR(B19/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <v>0.1</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
@@ -919,12 +919,12 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>(COUNTIF('CNG Feature Matrix'!E2:E103,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E103,"No"))</f>
-        <v>34</v>
+        <f>(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No"))</f>
+        <v>30</v>
       </c>
       <c r="C20" s="17">
         <f>IFERROR(B20/$B$7,0)</f>
-        <v>0.3333333333</v>
+        <v>0.2912621359223301</v>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1240,44 +1240,32 @@
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Provider-level configuration</t>
-        </is>
-      </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>NCRYPT_PIN_PROPERTY is implemented: the PIN is handed to the session layer, and because sessions open lazily a PIN set before the first cryptographic call is the one used to log in. Token selection is now writable too, by KSP_TOKEN_LABEL_PROPERTY or KSP_SLOT_PROPERTY, in the window between NCryptOpenStorageProvider and the first operation: the slot is bound on first use rather than during initialisation, so the choice is still open. After binding it is refused with NTE_INVALID_HANDLE rather than accepted and ignored, because PKCS#11 cannot move a session between tokens and a caller told its selection succeeded would keep using the old one. A selection naming no present token is an error, never a fallback. Verified against TWO real tokens with different labels, PINs and keys; a test with one token cannot distinguish a working selection from an ignored one.</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="I5" s="24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr"/>
+      <c r="I5" s="24" t="inlineStr"/>
       <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Vendor-specific</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
-        <is>
-          <t>NCRYPT_PIN_PROPERTY is implemented: the PIN is handed to the session layer, and because sessions open lazily a PIN set before the first cryptographic call is the one used to log in. Token selection is read-only through this call by design — the session pool is already bound to a slot by then and PKCS#11 cannot move a session between tokens, so accepting the value would be worse than refusing it. Choose the token with SOFTHSM2_SLOT or SOFTHSM2_TOKEN_LABEL and read it back with KSP_SLOT_PROPERTY.</t>
-        </is>
-      </c>
+      <c r="K5" s="25" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
@@ -3595,14 +3583,14 @@
           <t>RFC 3394 / 5649</t>
         </is>
       </c>
-      <c r="E53" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
@@ -3610,26 +3598,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H53" s="24" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H53" s="24" t="inlineStr"/>
+      <c r="I53" s="24" t="inlineStr"/>
       <c r="J53" s="25" t="inlineStr">
         <is>
           <t>Some HSMs (device)</t>
         </is>
       </c>
-      <c r="K53" s="25" t="inlineStr">
-        <is>
-          <t>Implemented both ways through BCRYPT_AES_WRAP_KEY_BLOB, gated on CKM_AES_KEY_WRAP. Unwrap works on any token: a key arrives wrapped under a KEK already on the token and is created sensitive and non-extractable, so wrapping is a way in and not a way back out. Wrap is Partial by consequence, not omission — C_WrapKey answers CKR_KEY_UNEXTRACTABLE for every key this provider generates, because they are all CKA_EXTRACTABLE=FALSE. It is useful only for a key the provider opened rather than created, on a token provisioned with extractable keys.</t>
-        </is>
-      </c>
+      <c r="K53" s="25" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr">
@@ -4195,41 +4171,29 @@
           <t>Raw symmetric key material</t>
         </is>
       </c>
-      <c r="E65" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H65" s="24" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="I65" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H65" s="24" t="inlineStr"/>
+      <c r="I65" s="24" t="inlineStr"/>
       <c r="J65" s="25" t="inlineStr">
         <is>
           <t>MS Software KSP</t>
         </is>
       </c>
-      <c r="K65" s="25" t="inlineStr">
-        <is>
-          <t>Import is implemented: BCRYPT_KEY_DATA_BLOB creates a CKO_SECRET_KEY via C_CreateObject with CKA_VALUE, AES for 16/24/32-byte material and a generic secret otherwise. Export is refused and will stay refused — every key this provider creates or imports is CKA_EXTRACTABLE=FALSE, which is the point of the HSM model. Making export work would mean creating extractable keys, weakening every deployment to satisfy one blob type.</t>
-        </is>
-      </c>
+      <c r="K65" s="25" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
@@ -5116,22 +5080,22 @@
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>LIFE-01</t>
+          <t>PROP-18</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
-          <t>Key lifecycle</t>
+          <t>Key properties</t>
         </is>
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>CreatePersistedKey</t>
+          <t>NCRYPT_EXPORT_POLICY_PROPERTY</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Immediate and deferred generation</t>
+          <t>Caller declares at creation whether a key may leave the token</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
@@ -5153,7 +5117,7 @@
       <c r="I84" s="21" t="inlineStr"/>
       <c r="J84" s="22" t="inlineStr">
         <is>
-          <t>All providers</t>
+          <t>MS Software KSP; every provider that supports key backup</t>
         </is>
       </c>
       <c r="K84" s="22" t="inlineStr"/>
@@ -5161,7 +5125,7 @@
     <row r="85">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>LIFE-02</t>
+          <t>LIFE-01</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
@@ -5171,12 +5135,12 @@
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>FinalizeKey</t>
+          <t>CreatePersistedKey</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>Deferred generation trigger</t>
+          <t>Immediate and deferred generation</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
@@ -5206,7 +5170,7 @@
     <row r="86">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>LIFE-03</t>
+          <t>LIFE-02</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
@@ -5216,12 +5180,12 @@
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>OpenKey by name</t>
+          <t>FinalizeKey</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Asymmetric and symmetric</t>
+          <t>Deferred generation trigger</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
@@ -5251,7 +5215,7 @@
     <row r="87">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>LIFE-04</t>
+          <t>LIFE-03</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
@@ -5261,12 +5225,12 @@
       </c>
       <c r="C87" s="24" t="inlineStr">
         <is>
-          <t>DeleteKey</t>
+          <t>OpenKey by name</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>Destroys all token objects</t>
+          <t>Asymmetric and symmetric</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
@@ -5296,7 +5260,7 @@
     <row r="88">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>LIFE-05</t>
+          <t>LIFE-04</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
@@ -5306,12 +5270,12 @@
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>EnumKeys</t>
+          <t>DeleteKey</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>Paged enumeration with state</t>
+          <t>Destroys all token objects</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
@@ -5341,7 +5305,7 @@
     <row r="89">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>LIFE-06</t>
+          <t>LIFE-05</t>
         </is>
       </c>
       <c r="B89" s="24" t="inlineStr">
@@ -5351,12 +5315,12 @@
       </c>
       <c r="C89" s="24" t="inlineStr">
         <is>
-          <t>EnumAlgorithms</t>
+          <t>EnumKeys</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>NCryptEnumAlgorithms support</t>
+          <t>Paged enumeration with state</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
@@ -5371,7 +5335,7 @@
       </c>
       <c r="G89" s="24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr"/>
@@ -5386,7 +5350,7 @@
     <row r="90">
       <c r="A90" s="21" t="inlineStr">
         <is>
-          <t>LIFE-07</t>
+          <t>LIFE-06</t>
         </is>
       </c>
       <c r="B90" s="21" t="inlineStr">
@@ -5396,12 +5360,12 @@
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>IsAlgSupported</t>
+          <t>EnumAlgorithms</t>
         </is>
       </c>
       <c r="D90" s="22" t="inlineStr">
         <is>
-          <t>NCryptIsAlgSupported</t>
+          <t>NCryptEnumAlgorithms support</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -5431,7 +5395,7 @@
     <row r="91">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>LIFE-08</t>
+          <t>LIFE-07</t>
         </is>
       </c>
       <c r="B91" s="24" t="inlineStr">
@@ -5441,22 +5405,22 @@
       </c>
       <c r="C91" s="24" t="inlineStr">
         <is>
-          <t>Machine vs user key scope</t>
+          <t>IsAlgSupported</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>NCRYPT_MACHINE_KEY_FLAG</t>
-        </is>
-      </c>
-      <c r="E91" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>NCryptIsAlgSupported</t>
+        </is>
+      </c>
+      <c r="E91" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F91" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G91" s="24" t="inlineStr">
@@ -5464,56 +5428,44 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H91" s="24" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="I91" s="24" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="H91" s="24" t="inlineStr"/>
+      <c r="I91" s="24" t="inlineStr"/>
       <c r="J91" s="25" t="inlineStr">
         <is>
           <t>All providers</t>
         </is>
       </c>
-      <c r="K91" s="25" t="inlineStr">
-        <is>
-          <t>NCRYPT_MACHINE_KEY_FLAG is honoured on CreatePersistedKey, OpenKey and EnumKeys: the scope becomes a CKA_LABEL prefix ("m/name" or "u/name"), so a machine key and a user key of the same name are distinct objects instead of silently aliasing. Enumeration filters by scope and reports unprefixed names. This is NAMESPACING, NOT ISOLATION — anyone who can log into the token can read either scope. Real isolation needs an ACL model PKCS#11 does not provide within a slot, and no amount of label work supplies one.</t>
-        </is>
-      </c>
+      <c r="K91" s="25" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>LIFE-08</t>
         </is>
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Key lifecycle</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>Hardware key protection</t>
+          <t>Machine vs user key scope</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>Tamper-resistant storage</t>
-        </is>
-      </c>
-      <c r="E92" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>NCRYPT_MACHINE_KEY_FLAG is honoured on CreatePersistedKey, OpenKey and EnumKeys. Within one token it is a CKA_LABEL prefix ("m/name" or "u/name"), which keeps distinct keys distinct and is NAMESPACING, NOT ISOLATION. Set KSP_MACHINE_TOKEN_LABEL and KSP_USER_TOKEN_LABEL (or the slot equivalents) and the flag instead selects WHICH TOKEN, each with its own PIN and its own session pool, so isolation is as strong as the token boundary PKCS#11 does have: a caller holding the user PIN cannot read machine keys because it cannot log in to read them. Setting only one of a pair, or two names resolving to one token, is refused rather than half-applied — isolation that reports success and does not isolate is worse than none. Unconfigured behaviour is unchanged. Verified against two real tokens with different PINs, including a case run WITHOUT the machine PIN in which the machine token must be unreachable.</t>
+        </is>
+      </c>
+      <c r="E92" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>Not covered</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
@@ -5521,31 +5473,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H92" s="21" t="inlineStr">
-        <is>
-          <t>Blocked: hardware / commercial</t>
-        </is>
-      </c>
-      <c r="I92" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H92" s="21" t="inlineStr"/>
+      <c r="I92" s="21" t="inlineStr"/>
       <c r="J92" s="22" t="inlineStr">
         <is>
-          <t>All commercial providers</t>
-        </is>
-      </c>
-      <c r="K92" s="22" t="inlineStr">
-        <is>
-          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
-        </is>
-      </c>
+          <t>All providers</t>
+        </is>
+      </c>
+      <c r="K92" s="22" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>OPS-02</t>
+          <t>OPS-01</t>
         </is>
       </c>
       <c r="B93" s="24" t="inlineStr">
@@ -5555,12 +5495,12 @@
       </c>
       <c r="C93" s="24" t="inlineStr">
         <is>
-          <t>FIPS 140-2/3 validation</t>
+          <t>Hardware key protection</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>Certified cryptographic module</t>
+          <t>Tamper-resistant storage</t>
         </is>
       </c>
       <c r="E93" s="27" t="inlineStr">
@@ -5575,7 +5515,7 @@
       </c>
       <c r="G93" s="24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H93" s="24" t="inlineStr">
@@ -5595,14 +5535,14 @@
       </c>
       <c r="K93" s="25" t="inlineStr">
         <is>
-          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
+          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>OPS-02</t>
         </is>
       </c>
       <c r="B94" s="21" t="inlineStr">
@@ -5612,12 +5552,12 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Authenticode-signed binary</t>
+          <t>FIPS 140-2/3 validation</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Commercial code-signing certificate</t>
+          <t>Certified cryptographic module</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
@@ -5632,7 +5572,7 @@
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
@@ -5652,14 +5592,14 @@
       </c>
       <c r="K94" s="22" t="inlineStr">
         <is>
-          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
+          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>OPS-03</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
@@ -5669,42 +5609,54 @@
       </c>
       <c r="C95" s="24" t="inlineStr">
         <is>
-          <t>Multiple slots / tokens</t>
+          <t>Authenticode-signed binary</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>Selecting among several tokens</t>
-        </is>
-      </c>
-      <c r="E95" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Commercial code-signing certificate</t>
+        </is>
+      </c>
+      <c r="E95" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F95" s="24" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Not covered</t>
         </is>
       </c>
       <c r="G95" s="24" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H95" s="24" t="inlineStr"/>
-      <c r="I95" s="24" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>Blocked: hardware / commercial</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J95" s="25" t="inlineStr">
         <is>
           <t>All commercial providers</t>
         </is>
       </c>
-      <c r="K95" s="25" t="inlineStr"/>
+      <c r="K95" s="25" t="inlineStr">
+        <is>
+          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>OPS-05</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="B96" s="21" t="inlineStr">
@@ -5714,22 +5666,22 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Key attestation</t>
+          <t>Multiple slots / tokens</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>TPM / HSM-signed key origin proof</t>
-        </is>
-      </c>
-      <c r="E96" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Selecting among several tokens</t>
+        </is>
+      </c>
+      <c r="E96" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>Not covered</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G96" s="21" t="inlineStr">
@@ -5737,31 +5689,19 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H96" s="21" t="inlineStr">
-        <is>
-          <t>Blocked: no PKCS#11 mechanism</t>
-        </is>
-      </c>
-      <c r="I96" s="21" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="H96" s="21" t="inlineStr"/>
+      <c r="I96" s="21" t="inlineStr"/>
       <c r="J96" s="22" t="inlineStr">
         <is>
-          <t>MS Platform Crypto; some HSMs</t>
-        </is>
-      </c>
-      <c r="K96" s="22" t="inlineStr">
-        <is>
-          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
-        </is>
-      </c>
+          <t>All commercial providers</t>
+        </is>
+      </c>
+      <c r="K96" s="22" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>OPS-06</t>
+          <t>OPS-05</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
@@ -5771,12 +5711,12 @@
       </c>
       <c r="C97" s="24" t="inlineStr">
         <is>
-          <t>Load balancing / HA</t>
+          <t>Key attestation</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>Multiple HSM members</t>
+          <t>TPM / HSM-signed key origin proof</t>
         </is>
       </c>
       <c r="E97" s="27" t="inlineStr">
@@ -5791,34 +5731,34 @@
       </c>
       <c r="G97" s="24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H97" s="24" t="inlineStr">
         <is>
-          <t>Blocked: hardware / commercial</t>
+          <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
       <c r="I97" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="J97" s="25" t="inlineStr">
         <is>
-          <t>Thales; Entrust</t>
+          <t>MS Platform Crypto; some HSMs</t>
         </is>
       </c>
       <c r="K97" s="25" t="inlineStr">
         <is>
-          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
+          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>OPS-07</t>
+          <t>OPS-06</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
@@ -5828,42 +5768,54 @@
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>Session pool concurrency</t>
+          <t>Load balancing / HA</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Concurrent NCrypt calls</t>
-        </is>
-      </c>
-      <c r="E98" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Multiple HSM members</t>
+        </is>
+      </c>
+      <c r="E98" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Not covered</t>
         </is>
       </c>
       <c r="G98" s="21" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H98" s="21" t="inlineStr"/>
-      <c r="I98" s="21" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H98" s="21" t="inlineStr">
+        <is>
+          <t>Blocked: hardware / commercial</t>
+        </is>
+      </c>
+      <c r="I98" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J98" s="22" t="inlineStr">
         <is>
-          <t>All providers</t>
-        </is>
-      </c>
-      <c r="K98" s="22" t="inlineStr"/>
+          <t>Thales; Entrust</t>
+        </is>
+      </c>
+      <c r="K98" s="22" t="inlineStr">
+        <is>
+          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>OPS-08</t>
+          <t>OPS-07</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
@@ -5873,12 +5825,12 @@
       </c>
       <c r="C99" s="24" t="inlineStr">
         <is>
-          <t>Re-initialisation without restart</t>
+          <t>Session pool concurrency</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>Recover from a bad DLL path</t>
+          <t>Concurrent NCrypt calls</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
@@ -5900,7 +5852,7 @@
       <c r="I99" s="24" t="inlineStr"/>
       <c r="J99" s="25" t="inlineStr">
         <is>
-          <t>Vendor-specific</t>
+          <t>All providers</t>
         </is>
       </c>
       <c r="K99" s="25" t="inlineStr"/>
@@ -5908,7 +5860,7 @@
     <row r="100">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>OPS-09</t>
+          <t>OPS-08</t>
         </is>
       </c>
       <c r="B100" s="21" t="inlineStr">
@@ -5918,12 +5870,12 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>PIN caching / re-login</t>
+          <t>Re-initialisation without restart</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Session recovery after token logout</t>
+          <t>Recover from a bad DLL path</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -5938,14 +5890,14 @@
       </c>
       <c r="G100" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H100" s="21" t="inlineStr"/>
       <c r="I100" s="21" t="inlineStr"/>
       <c r="J100" s="22" t="inlineStr">
         <is>
-          <t>All commercial providers</t>
+          <t>Vendor-specific</t>
         </is>
       </c>
       <c r="K100" s="22" t="inlineStr"/>
@@ -5953,7 +5905,7 @@
     <row r="101">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>OPS-10</t>
+          <t>OPS-09</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
@@ -5963,12 +5915,12 @@
       </c>
       <c r="C101" s="24" t="inlineStr">
         <is>
-          <t>Logging / diagnostics</t>
+          <t>PIN caching / re-login</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>Trace output for support</t>
+          <t>Session recovery after token logout</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -5983,14 +5935,14 @@
       </c>
       <c r="G101" s="24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr"/>
       <c r="I101" s="24" t="inlineStr"/>
       <c r="J101" s="25" t="inlineStr">
         <is>
-          <t>All providers</t>
+          <t>All commercial providers</t>
         </is>
       </c>
       <c r="K101" s="25" t="inlineStr"/>
@@ -5998,7 +5950,7 @@
     <row r="102">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>OPS-13</t>
+          <t>OPS-10</t>
         </is>
       </c>
       <c r="B102" s="21" t="inlineStr">
@@ -6008,12 +5960,12 @@
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>Runtime capability discovery</t>
+          <t>Logging / diagnostics</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Advertised algorithms reflect what the token implements, not a compiled-in list</t>
+          <t>Trace output for support</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
@@ -6035,7 +5987,7 @@
       <c r="I102" s="21" t="inlineStr"/>
       <c r="J102" s="22" t="inlineStr">
         <is>
-          <t>All commercial providers (implicit — each ships for its own device)</t>
+          <t>All providers</t>
         </is>
       </c>
       <c r="K102" s="22" t="inlineStr"/>
@@ -6043,7 +5995,7 @@
     <row r="103">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>OPS-14</t>
+          <t>OPS-13</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
@@ -6053,12 +6005,12 @@
       </c>
       <c r="C103" s="24" t="inlineStr">
         <is>
-          <t>Backend portability</t>
+          <t>Runtime capability discovery</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>Any PKCS#11 v2.40+ module can back the provider (KSP_PKCS11_LIB)</t>
+          <t>Advertised algorithms reflect what the token implements, not a compiled-in list</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
@@ -6080,13 +6032,58 @@
       <c r="I103" s="24" t="inlineStr"/>
       <c r="J103" s="25" t="inlineStr">
         <is>
+          <t>All commercial providers (implicit — each ships for its own device)</t>
+        </is>
+      </c>
+      <c r="K103" s="25" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>OPS-14</t>
+        </is>
+      </c>
+      <c r="B104" s="21" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="C104" s="21" t="inlineStr">
+        <is>
+          <t>Backend portability</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>Any PKCS#11 v2.40+ module can back the provider (KSP_PKCS11_LIB)</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="G104" s="21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H104" s="21" t="inlineStr"/>
+      <c r="I104" s="21" t="inlineStr"/>
+      <c r="J104" s="22" t="inlineStr">
+        <is>
           <t>Not offered — commercial providers are bound to their own hardware</t>
         </is>
       </c>
-      <c r="K103" s="25" t="inlineStr"/>
+      <c r="K104" s="22" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K103"/>
+  <autoFilter ref="A1:K104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6154,20 +6151,20 @@
         </is>
       </c>
       <c r="B4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A4,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A4,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A4,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>1</v>
       </c>
       <c r="E4" s="15">
         <f>SUM(B4:D4)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="F4" s="12">
         <f>IFERROR(B4/E4,0)</f>
@@ -6181,20 +6178,20 @@
         </is>
       </c>
       <c r="B5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A5,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>6</v>
       </c>
       <c r="C5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A5,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A5,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E5" s="15">
         <f>SUM(B5:D5)</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="F5" s="12">
         <f>IFERROR(B5/E5,0)</f>
@@ -6208,24 +6205,24 @@
         </is>
       </c>
       <c r="B6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A6,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>1</v>
       </c>
       <c r="C6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A6,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>2</v>
       </c>
       <c r="D6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A6,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E6" s="15">
         <f>SUM(B6:D6)</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="F6" s="12">
         <f>IFERROR(B6/E6,0)</f>
-        <v>0.3333333333</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -6235,24 +6232,24 @@
         </is>
       </c>
       <c r="B7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A7,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>11</v>
       </c>
       <c r="C7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A7,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A7,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E7" s="15">
         <f>SUM(B7:D7)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="F7" s="12">
         <f>IFERROR(B7/E7,0)</f>
-        <v>0.9166666667</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -6262,24 +6259,24 @@
         </is>
       </c>
       <c r="B8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A8,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>5</v>
       </c>
       <c r="C8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A8,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A8,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>1</v>
       </c>
       <c r="E8" s="15">
         <f>SUM(B8:D8)</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="F8" s="12">
         <f>IFERROR(B8/E8,0)</f>
-        <v>0.8333333333</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -6289,24 +6286,24 @@
         </is>
       </c>
       <c r="B9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A9,'CNG Feature Matrix'!E2:E103,"Yes")</f>
-        <v>5</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>6</v>
       </c>
       <c r="C9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A9,'CNG Feature Matrix'!E2:E103,"Partial")</f>
-        <v>1</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <v>0</v>
       </c>
       <c r="D9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A9,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>4</v>
       </c>
       <c r="E9" s="15">
         <f>SUM(B9:D9)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F9" s="12">
         <f>IFERROR(B9/E9,0)</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -6316,24 +6313,24 @@
         </is>
       </c>
       <c r="B10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A10,'CNG Feature Matrix'!E2:E103,"Yes")</f>
-        <v>7</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>8</v>
       </c>
       <c r="C10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A10,'CNG Feature Matrix'!E2:E103,"Partial")</f>
-        <v>1</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <v>0</v>
       </c>
       <c r="D10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A10,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E10" s="15">
         <f>SUM(B10:D10)</f>
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="F10" s="12">
         <f>IFERROR(B10/E10,0)</f>
-        <v>0.875</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -6343,24 +6340,24 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A11,'CNG Feature Matrix'!E2:E103,"Yes")</f>
-        <v>12</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>13</v>
       </c>
       <c r="C11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A11,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A11,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>4</v>
       </c>
       <c r="E11" s="15">
         <f>SUM(B11:D11)</f>
-        <v>16</v>
+        <v>17.0</v>
       </c>
       <c r="F11" s="12">
         <f>IFERROR(B11/E11,0)</f>
-        <v>0.75</v>
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="12">
@@ -6370,24 +6367,24 @@
         </is>
       </c>
       <c r="B12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A12,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>7</v>
       </c>
       <c r="C12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A12,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A12,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>5</v>
       </c>
       <c r="E12" s="15">
         <f>SUM(B12:D12)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="F12" s="12">
         <f>IFERROR(B12/E12,0)</f>
-        <v>0.5833333333</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -6397,20 +6394,20 @@
         </is>
       </c>
       <c r="B13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A13,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A13,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A13,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>2</v>
       </c>
       <c r="E13" s="15">
         <f>SUM(B13:D13)</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="F13" s="12">
         <f>IFERROR(B13/E13,0)</f>
@@ -6424,24 +6421,24 @@
         </is>
       </c>
       <c r="B14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A14,'CNG Feature Matrix'!E2:E103,"Yes")</f>
-        <v>6</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>7</v>
       </c>
       <c r="C14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A14,'CNG Feature Matrix'!E2:E103,"Partial")</f>
-        <v>4</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <v>3</v>
       </c>
       <c r="D14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A14,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>2</v>
       </c>
       <c r="E14" s="15">
         <f>SUM(B14:D14)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="F14" s="12">
         <f>IFERROR(B14/E14,0)</f>
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -6451,24 +6448,24 @@
         </is>
       </c>
       <c r="B15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A15,'CNG Feature Matrix'!E2:E103,"Yes")</f>
-        <v>7</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>8</v>
       </c>
       <c r="C15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A15,'CNG Feature Matrix'!E2:E103,"Partial")</f>
-        <v>3</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <v>2</v>
       </c>
       <c r="D15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A15,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E15" s="15">
         <f>SUM(B15:D15)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="12">
         <f>IFERROR(B15/E15,0)</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
@@ -6478,20 +6475,20 @@
         </is>
       </c>
       <c r="B16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A16,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>1</v>
       </c>
       <c r="C16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A16,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A16,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E16" s="15">
         <f>SUM(B16:D16)</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="F16" s="12">
         <f>IFERROR(B16/E16,0)</f>
@@ -6505,20 +6502,20 @@
         </is>
       </c>
       <c r="B17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A17,'CNG Feature Matrix'!E2:E103,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A17,'CNG Feature Matrix'!E2:E103,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B103,$A17,'CNG Feature Matrix'!E2:E103,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>1</v>
       </c>
       <c r="E17" s="15">
         <f>SUM(B17:D17)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="F17" s="12">
         <f>IFERROR(B17/E17,0)</f>
@@ -6533,23 +6530,23 @@
       </c>
       <c r="B18" s="7">
         <f>SUM(B4:B17)</f>
-        <v>68</v>
+        <v>73.0</v>
       </c>
       <c r="C18" s="7">
         <f>SUM(C4:C17)</f>
-        <v>14</v>
+        <v>10.0</v>
       </c>
       <c r="D18" s="7">
         <f>SUM(D4:D17)</f>
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(E4:E17)</f>
-        <v>102</v>
+        <v>103.0</v>
       </c>
       <c r="F18" s="17">
         <f>IFERROR(B18/E18,0)</f>
-        <v>0.6666666667</v>
+        <v>0.7087378640776699</v>
       </c>
     </row>
   </sheetData>
@@ -6563,7 +6560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7355,22 +7352,22 @@
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>AES-09</t>
+          <t>DSA-01</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Symmetric AES</t>
+          <t>Asymmetric DSA</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>AES key wrap</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>DSA signing</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -7380,29 +7377,29 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>Implemented both ways through BCRYPT_AES_WRAP_KEY_BLOB, gated on CKM_AES_KEY_WRAP. Unwrap works on any token: a key arrives wrapped under a KEK already on the token and is created sensitive and non-extractable, so wrapping is a way in and not a way back out. Wrap is Partial by consequence, not omission — C_WrapKey answers CKR_KEY_UNEXTRACTABLE for every key this provider generates, because they are all CKA_EXTRACTABLE=FALSE. It is useful only for a key the provider opened rather than created, on a token provisioned with extractable keys.</t>
+          <t>Deliberately out of scope. Deprecated in modern Windows PKI and absent from every HSM KSP surveyed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>DSA-01</t>
+          <t>ECDH-06</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Asymmetric DSA</t>
+          <t>Key agreement</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>DSA signing</t>
+          <t>Finite-field Diffie-Hellman</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -7422,24 +7419,24 @@
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>Deliberately out of scope. Deprecated in modern Windows PKI and absent from every HSM KSP surveyed.</t>
+          <t>Out of scope by choice. ECDH supersedes it and no surveyed HSM KSP exposes it. Would need CKM_DH_PKCS_KEY_PAIR_GEN plus CKM_DH_PKCS_DERIVE.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>ECDH-06</t>
+          <t>FMT-06</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Key agreement</t>
+          <t>Key formats</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Finite-field Diffie-Hellman</t>
+          <t>Private key export</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -7454,19 +7451,19 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>Out of scope by choice. ECDH supersedes it and no surveyed HSM KSP exposes it. Would need CKM_DH_PKCS_KEY_PAIR_GEN plus CKM_DH_PKCS_DERIVE.</t>
+          <t>Refused by design with NTE_NOT_SUPPORTED. Keys are CKA_EXTRACTABLE=FALSE. This is correct HSM behaviour not a gap.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>FMT-06</t>
+          <t>FMT-07</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
@@ -7476,7 +7473,7 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Private key export</t>
+          <t>Private key import</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
@@ -7491,19 +7488,19 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>Refused by design with NTE_NOT_SUPPORTED. Keys are CKA_EXTRACTABLE=FALSE. This is correct HSM behaviour not a gap.</t>
+          <t>Returns NTE_NOT_SUPPORTED. Would need C_CreateObject with private material or C_UnwrapKey. Contradicts the HSM posture; only add if a migration workflow demands it.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>FMT-07</t>
+          <t>FMT-09</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
@@ -7513,7 +7510,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Private key import</t>
+          <t>PKCS#8 blob</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -7533,29 +7530,29 @@
       </c>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>Returns NTE_NOT_SUPPORTED. Would need C_CreateObject with private material or C_UnwrapKey. Contradicts the HSM posture; only add if a migration workflow demands it.</t>
+          <t>Same constraint as FMT-07: it is a private-key format and keys are non-extractable.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>FMT-08</t>
+          <t>IFACE-06</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Key formats</t>
+          <t>Provider interface</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>BCRYPT_KEY_DATA_BLOB</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>GetOperationProperty</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -7565,29 +7562,29 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>Import is implemented: BCRYPT_KEY_DATA_BLOB creates a CKO_SECRET_KEY via C_CreateObject with CKA_VALUE, AES for 16/24/32-byte material and a generic secret otherwise. Export is refused and will stay refused — every key this provider creates or imports is CKA_EXTRACTABLE=FALSE, which is the point of the HSM model. Making export work would mean creating extractable keys, weakening every deployment to satisfy one blob type.</t>
+          <t>Returns NTE_NOT_SUPPORTED. Only needed for overlapped I/O; PKCS#11 is synchronous so there is nothing to report.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>FMT-09</t>
+          <t>IFACE-07</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Key formats</t>
+          <t>Provider interface</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>PKCS#8 blob</t>
+          <t>PromptUser</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -7607,29 +7604,29 @@
       </c>
       <c r="G28" s="22" t="inlineStr">
         <is>
-          <t>Same constraint as FMT-07: it is a private-key format and keys are non-extractable.</t>
+          <t>Returns NTE_NOT_SUPPORTED. Would need a UI thread and a window handle from NCRYPT_WINDOW_HANDLE_PROPERTY.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>IFACE-04</t>
+          <t>PROP-12</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Provider interface</t>
+          <t>Key properties</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>SetProviderProperty</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>NCRYPT_UI_POLICY_PROPERTY</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -7639,29 +7636,29 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>NCRYPT_PIN_PROPERTY is implemented: the PIN is handed to the session layer, and because sessions open lazily a PIN set before the first cryptographic call is the one used to log in. Token selection is read-only through this call by design — the session pool is already bound to a slot by then and PKCS#11 cannot move a session between tokens, so accepting the value would be worse than refusing it. Choose the token with SOFTHSM2_SLOT or SOFTHSM2_TOKEN_LABEL and read it back with KSP_SLOT_PROPERTY.</t>
+          <t>Depends on PromptUser (IFACE-07). Same UI-thread requirement.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t>IFACE-06</t>
+          <t>PROP-15</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Provider interface</t>
+          <t>Key properties</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>GetOperationProperty</t>
+          <t>NCRYPT_WINDOW_HANDLE_PROPERTY</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -7681,29 +7678,29 @@
       </c>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>Returns NTE_NOT_SUPPORTED. Only needed for overlapped I/O; PKCS#11 is synchronous so there is nothing to report.</t>
+          <t>Only meaningful with PromptUser (IFACE-07).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>IFACE-07</t>
+          <t>RSA-02</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Provider interface</t>
+          <t>Asymmetric RSA</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>PromptUser</t>
-        </is>
-      </c>
-      <c r="D31" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>RSA 1024 and below</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -7713,165 +7710,17 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>Returns NTE_NOT_SUPPORTED. Would need a UI thread and a window handle from NCRYPT_WINDOW_HANDLE_PROPERTY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>LIFE-08</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>Key lifecycle</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Machine vs user key scope</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr">
-        <is>
-          <t>NCRYPT_MACHINE_KEY_FLAG is honoured on CreatePersistedKey, OpenKey and EnumKeys: the scope becomes a CKA_LABEL prefix ("m/name" or "u/name"), so a machine key and a user key of the same name are distinct objects instead of silently aliasing. Enumeration filters by scope and reports unprefixed names. This is NAMESPACING, NOT ISOLATION — anyone who can log into the token can read either scope. Real isolation needs an ACL model PKCS#11 does not provide within a slot, and no amount of label work supplies one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>PROP-12</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>Key properties</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>NCRYPT_UI_POLICY_PROPERTY</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E33" s="24" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="F33" s="24" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G33" s="25" t="inlineStr">
-        <is>
-          <t>Depends on PromptUser (IFACE-07). Same UI-thread requirement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>PROP-15</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Key properties</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>NCRYPT_WINDOW_HANDLE_PROPERTY</t>
-        </is>
-      </c>
-      <c r="D34" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr">
-        <is>
-          <t>Only meaningful with PromptUser (IFACE-07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>RSA-02</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Asymmetric RSA</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>RSA 1024 and below</t>
-        </is>
-      </c>
-      <c r="D35" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="inlineStr">
-        <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
           <t>Build-time opt-in only. KSP_RSA_MIN_BITS defaults to 2048; a legacy build can lower it, but the shipped default still rejects &lt;2048 with NTE_BAD_LEN. Deliberate: silently allowing 1024 would weaken every deployment.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35"/>
+  <autoFilter ref="A1:G31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8028,7 +7877,7 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>22 unit suites, 1623 assertions, Linux/GCC against a controllable PKCS#11 mock. Pins down the provider's logic; cannot validate assumptions about real tokens.</t>
+          <t>22 unit suites, 1816 assertions, Linux/GCC against a controllable PKCS#11 mock. Pins down the provider's logic; cannot validate assumptions about real tokens.</t>
         </is>
       </c>
     </row>
@@ -8040,7 +7889,7 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>The same provider sources against Kryoptic, an independent PKCS#11 token in Rust. 230 assertions, run twice against one token so anything left behind is caught. Plus 33 concurrency assertions across 32 threads, and ThreadSanitizer.</t>
+          <t>The same provider sources against Kryoptic, an independent PKCS#11 token in Rust. 256 assertions, run twice against one token so anything left behind is caught. Plus 33 concurrency assertions across 32 threads under ThreadSanitizer, and - behind TWO tokens on one module - 53 for token selection and 28 for per-scope isolation, because a single token cannot tell a working selection from an ignored one.</t>
         </is>
       </c>
     </row>

--- a/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
+++ b/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Items'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Items'!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,9 +110,20 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -179,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -266,7 +277,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -666,7 +686,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-10-01   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
+          <t>As of 2026-10-02   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
         </is>
       </c>
     </row>
@@ -820,11 +840,11 @@
       </c>
       <c r="B15" s="15">
         <f>COUNTIF('CNG Feature Matrix'!H2:H104,A15)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="12">
         <f>IFERROR(B15/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
-        <v>0.4</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
@@ -840,11 +860,11 @@
       </c>
       <c r="B16" s="15">
         <f>COUNTIF('CNG Feature Matrix'!H2:H104,A16)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="12">
         <f>IFERROR(B16/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
-        <v>0.2</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
@@ -1362,7 +1382,7 @@
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>Deliberate position</t>
+          <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
       <c r="I7" s="24" t="inlineStr">
@@ -6560,16 +6580,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="110" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+    <col width="78" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6600,10 +6623,25 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>Outside this repo?</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>What works today</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>What the blocker rests on</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>What would actually close it</t>
         </is>
@@ -6635,12 +6673,27 @@
           <t>Blocked: needs ncrypt_provider.h / Windows</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>MSVC compiles nine of the ten source files clean at /W3 /WX and links test_p11_layer.exe. The mingw cross-compile is clean on all ten minus ksp_main.c.</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>ncrypt_provider.h, which declares NCRYPT_KEY_STORAGE_FUNCTION_TABLE. A dir /s /b across C: and D: on a windows-latest runner returned only this repository's own test mock, after a WDK install that reported success. It is not in the Windows SDK.</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>Phase 0 fixed all six root causes. MSVC compiles nine of the ten source files clean at /W3 /WX and links test_p11_layer. ksp_main.c cannot be built in hosted CI: ncrypt_provider.h does not exist on a windows-latest runner, established by a dir /s /b across C: and D: that returned only this repo's own test mock, after a WDK install that reported success. Needs a machine that has the header.</t>
         </is>
@@ -6672,12 +6725,27 @@
           <t>Blocked: needs ncrypt_provider.h / Windows</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>ML-DSA generates, reopens by parameter set and signs at all three sets, verified against Kryoptic built with its pqc feature over OpenSSL 3.5.8. Gated on the capability probe, so it is dark on SoftHSM2 and live on a v3.2 token.</t>
+        </is>
+      </c>
+      <c r="I3" s="25" t="inlineStr">
+        <is>
+          <t>The CNG post-quantum key blob layout, which is in a Windows SDK header not available here. Public key export is the only thing missing. A guessed layout would pass every test here and fail only on Windows — the BCRYPT_SHA224_ALGORITHM mistake exactly.</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="inlineStr">
         <is>
           <t>ML-DSA is wired through the KSP and gated on the capability probe: mechanism resolution, CKA_PARAMETER_SET key generation for all three parameter sets, key reopen, and signing. Verified end to end in session 10 against Kryoptic built with its pqc feature over OpenSSL 3.5.8 — generation, reopen by parameter set, and signature at the exact size for ML-DSA-44/65/87. Unreachable on SoftHSM2 2.7.0, which defines the mechanisms and implements none of them. Still Partial for one reason only: public key export is refused, because the CNG post-quantum key blob layout is in a Windows SDK header not available here. That is the same blocker as BUILD-01 and no backend fixes it.</t>
         </is>
@@ -6709,12 +6777,27 @@
           <t>Blocked: needs ncrypt_provider.h / Windows</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>Designated initialisers make a wrong slot NAME a build error. Eight provider-scoped slots are also signature-checked against &lt;ncrypt.h&gt;, which is what caught KSP_NotifyChangeKey holding an NCRYPT_KEY_HANDLE where the parameter is HANDLE *phEvent.</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>The same missing header. Key-scoped slots cannot be checked against the public prototype, because it is not the slot's shape: NCryptSignHash takes (hKey, ...) while the slot takes (hProvider, hKey, ...). Asserting the public shape there would be inventing a fact.</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>The table uses designated initialisers, so the SDK header assigns slots by name and a wrong NAME is a build error. Since session 14 eight provider-scoped slots are also signature-checked: their KSP prototype equals the documented public NCrypt one, so test_function_table.c assigns each to a pointer type copied from &lt;ncrypt.h&gt; and the build promotes incompatible-pointer-types to an error. That caught KSP_NotifyChangeKey taking an NCRYPT_KEY_HANDLE where the parameter is HANDLE *phEvent. Key-scoped slots cannot be checked this way - NCryptSignHash takes (hKey, ...) while the slot takes (hProvider, hKey, ...) - so full confirmation still needs ncrypt_provider.h.</t>
         </is>
@@ -6746,12 +6829,27 @@
           <t>Blocked: CNG has no identifier or slot</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>AES-CTR encrypts and decrypts, verified against a live token, selected through NCRYPT_CHAINING_MODE_PROPERTY.</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>CNG defines no counter-mode chaining string, so ChainingModeCTR is a provider extension that no stock application will select.</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Works but ChainingModeCTR is a KSP extension. CNG defines no standard counter-mode string so no stock application will select it.</t>
         </is>
@@ -6783,12 +6881,27 @@
           <t>Blocked: CNG has no identifier or slot</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Ed25519 signs, and is verified end to end against Kryoptic. The absent CK_EDDSA_PARAMS that selects the pure context-free form is deliberate and fault-injected.</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>CNG defines no EdDSA algorithm identifier at all, so EDDSA_ED25519 is this provider's own string and no stock application will ask for it. Nothing in the KSP can change that.</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>Works against SoftHSM2 AND verified end to end against Kryoptic (session 10), but uses the non-standard identifier EDDSA_ED25519. CNG defines no EdDSA algorithm ID so no stock application can request it. Nothing to fix in the KSP; blocked on Microsoft.</t>
         </is>
@@ -6820,12 +6933,27 @@
           <t>Blocked: CNG has no identifier or slot</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>Ed448 signs against Kryoptic with CK_EDDSA_PARAMS supplied, which Ed448 requires and Ed25519 must not have. The asymmetry is deliberate and both mistakes are fault-injected. It did NOT work before session 10: SoftHSM2 tolerates the missing parameter, so a second token was needed to see it.</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>Same as EDDSA-01 — no CNG identifier exists.</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t>Same constraint as EDDSA-01. Note that Ed448 signing did not in fact work until session 10: CKM_EDDSA requires CK_EDDSA_PARAMS for Ed448 and the provider sent none. SoftHSM2 tolerates its absence, so this was invisible until a second token refused it.</t>
         </is>
@@ -6857,12 +6985,27 @@
           <t>Blocked: CNG has no identifier or slot</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>HMAC signing works over CKM_SHA*_HMAC for SHA-1 through SHA-512, verified against a live token. It had never actually worked before session 10 — KSP_SignHash passed hPrivKey unconditionally and secret keys live in hSecretKey.</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>CNG reaches HMAC through BCrypt algorithm handles, not through KSP key algorithms, so HMAC_SHA* are this provider's own identifiers.</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>Works against SoftHSM2 but HMAC_SHA* are our own identifiers. CNG does HMAC through BCrypt algorithm handles not KSP key algorithms.</t>
         </is>
@@ -6894,12 +7037,27 @@
           <t>Blocked: CNG has no identifier or slot</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>The probe recognises CKM_ML_KEM, so the backend is not the obstacle. Nothing is advertised, deliberately.</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>The function table has no slot for encapsulation or decapsulation, so a KSP could hold an ML-KEM key with no entry point to use it. Whether a newer ncrypt_provider.h adds such slots cannot be established here — the same missing header.</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="inlineStr">
         <is>
           <t>NOT the same blocker as PQC-01. The probe recognises CKM_ML_KEM, so the backend is not what stops this: encapsulation and decapsulation have no slot in the NCRYPT_KEY_STORAGE_FUNCTION_TABLE this provider implements, so a KSP can hold an ML-KEM key with no entry point to use it. Whether a newer ncrypt_provider.h adds such slots cannot be determined here — same missing header as BUILD-01.</t>
         </is>
@@ -6931,12 +7089,27 @@
           <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Nothing. Not advertised.</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>OPAQUETRANSPORT has no defined wrapping format to follow, so there is no standard to implement against — only a format this provider would invent and no one else could read.</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>Would let keys move between instances of the same provider. Needs a defined wrapping format; no standard to follow.</t>
         </is>
@@ -6968,12 +7141,27 @@
           <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>Validates the provider and flags, clears *phEvent and refuses registration with NTE_NOT_SUPPORTED. Unregistering succeeds, because there is nothing to tear down. Before session 14 it returned ERROR_SUCCESS without writing the handle, so a caller waited on an uninitialised HANDLE.</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>PKCS#11 has no object-change channel: there is no C_WaitForSlotEvent equivalent for objects. Polling C_FindObjects on a timer would be a fabrication dressed as a notification. THIS IS THE ROW CLOSEST IN SHAPE TO the three that were wrongly called deliberate — it would become actionable the moment a backend offered such a channel, so it is worth re-reading rather than inheriting.</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
         <is>
           <t>Was a no-op returning ERROR_SUCCESS with the caller's HANDLE never written, so an application registering for notification was told it had succeeded and then waited on an uninitialised handle. It now validates the provider and the flags, clears *phEvent and refuses registration with NTE_NOT_SUPPORTED; unregistering succeeds because there is nothing to tear down. Real support needs a key-change channel a PKCS#11 token does not have - there is no C_WaitForSlotEvent equivalent for objects, and polling C_FindObjects on a timer would be a fabrication rather than a notification.</t>
         </is>
@@ -6982,17 +7170,17 @@
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>OPS-05</t>
+          <t>IFACE-06</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Provider interface</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Key attestation</t>
+          <t>GetOperationProperty</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
@@ -7005,31 +7193,46 @@
           <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
-        <is>
-          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Refused with NTE_NOT_SUPPORTED.</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>The property reports on an asynchronous operation and PKCS#11 is synchronous, so there is no operation state to report however much code is written. This row sat in the deliberate column until the pairing check was run against its own text, which already said "a fact about PKCS#11 rather than about this code" — so it was mislabelled by the person who wrote the reason, and the cross-check is what caught it.</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Returns NTE_NOT_SUPPORTED. Only needed for overlapped I/O; PKCS#11 is synchronous so there is nothing to report.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>PQC-03</t>
+          <t>OPS-05</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Post-quantum</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>LMS / XMSS</t>
+          <t>Key attestation</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
@@ -7042,31 +7245,46 @@
           <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
-        <is>
-          <t>Blocked at the backend, unlike PQC-01: no PKCS#11 v3.2 token surveyed implements LMS or XMSS. Stateful schemes also need one-time-key state persistence the KSP has no model for, and a lost state update forges signatures.</t>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>Nothing. Not advertised.</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t>Key attestation has no standard PKCS#11 mechanism. It is vendor-specific, so it is unreachable through a portable PKCS#11 layer by construction.</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="inlineStr">
+        <is>
+          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>PROP-11</t>
+          <t>PQC-03</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Key properties</t>
+          <t>Post-quantum</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>NCRYPT_SECURITY_DESCR_PROPERTY</t>
+          <t>LMS / XMSS</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
@@ -7079,21 +7297,36 @@
           <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>Returns NTE_NOT_SUPPORTED. PKCS#11 has no ACL model; would need a side-channel store mapping key labels to SDDL strings.</t>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>Nothing. Not advertised.</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>No PKCS#11 v3.2 token surveyed implements LMS or XMSS, so unlike PQC-01 this is blocked at the backend. The stateful schemes also need one-time-key state persistence the KSP has no model for, and a lost state update forges signatures — a correctness hazard, not just missing code.</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Blocked at the backend, unlike PQC-01: no PKCS#11 v3.2 token surveyed implements LMS or XMSS. Stateful schemes also need one-time-key state persistence the KSP has no model for, and a lost state update forges signatures.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>PROP-16</t>
+          <t>PROP-11</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
@@ -7103,7 +7336,7 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>NCRYPT_USE_COUNT_PROPERTY</t>
+          <t>NCRYPT_SECURITY_DESCR_PROPERTY</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
@@ -7116,31 +7349,46 @@
           <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
-        <is>
-          <t>Would need a counter object on the token incremented per operation. SoftHSM2 has no atomic counter primitive.</t>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>Refused with NTE_NOT_SUPPORTED rather than accepted and ignored.</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>PKCS#11 has no ACL model, so there is nothing to map an SDDL string onto. A side store from key label to descriptor would be this provider inventing an access control system it cannot enforce.</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="inlineStr">
+        <is>
+          <t>Returns NTE_NOT_SUPPORTED. PKCS#11 has no ACL model; would need a side-channel store mapping key labels to SDDL strings.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>PROP-16</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Key properties</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Hardware key protection</t>
+          <t>NCRYPT_USE_COUNT_PROPERTY</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
@@ -7150,24 +7398,39 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>Blocked: hardware / commercial</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
+          <t>Blocked: no PKCS#11 mechanism</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>Refused with NTE_NOT_SUPPORTED.</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>No atomic counter primitive in PKCS#11 or SoftHSM2. A read-modify-write on an object attribute is not a use count under concurrency, and a wrong count is worse than no count.</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Would need a counter object on the token incremented per operation. SoftHSM2 has no atomic counter primitive.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>OPS-02</t>
+          <t>OPS-01</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
@@ -7177,7 +7440,7 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>FIPS 140-2/3 validation</t>
+          <t>Hardware key protection</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
@@ -7190,21 +7453,36 @@
           <t>Blocked: hardware / commercial</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
-        <is>
-          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>Nothing, and it cannot: SoftHSM2 is a software token over encrypted SQLite. The provider reports NCRYPT_IMPL_SOFTWARE_FLAG, truthfully — it used to say hardware in the source while emitting the software value.</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Hardware. The PKCS#11 abstraction already allows pointing the KSP at a real HSM, so this closes by deployment rather than by code.</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="inlineStr">
+        <is>
+          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>OPS-02</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
@@ -7214,7 +7492,7 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Authenticode-signed binary</t>
+          <t>FIPS 140-2/3 validation</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
@@ -7227,21 +7505,36 @@
           <t>Blocked: hardware / commercial</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>Certified hardware and a formal validation programme. Follows from OPS-01 and is not an engineering task.</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>OPS-06</t>
+          <t>OPS-03</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
@@ -7251,7 +7544,7 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Load balancing / HA</t>
+          <t>Authenticode-signed binary</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
@@ -7264,31 +7557,46 @@
           <t>Blocked: hardware / commercial</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
-        <is>
-          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>The signing pipeline is complete and self-tested: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX whose password comes from the environment and never a parameter, or Azure Trusted Signing. CI signs automatically once the secret exists.</t>
+        </is>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>An OV or EV code-signing certificate, which must be bought by a verified legal entity. Nothing in this repository can supply that, so the shipped binary is unsigned and the row stays Not covered.</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="inlineStr">
+        <is>
+          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>3DES-01</t>
+          <t>OPS-06</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Symmetric legacy</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>3DES / DES</t>
+          <t>Load balancing / HA</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -7298,39 +7606,54 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>Deliberate position</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
-        <is>
-          <t>Deliberately out of scope. Deprecated and excluded from modern HLK requirements despite SoftHSM2 supporting 14 DES mechanisms.</t>
+          <t>Blocked: hardware / commercial</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>Nothing here, and nothing needs to: it is handled inside vendor PKCS#11 libraries.</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>A vendor library. The provider inherits load balancing and failover automatically when pointed at one, so there is nothing to implement.</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>AES-08</t>
+          <t>3DES-01</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Symmetric AES</t>
+          <t>Symmetric legacy</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>AES-CFB</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>3DES / DES</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -7338,36 +7661,51 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>Implemented and verified against a live token for both feedback sizes CNG can reach: the 8-bit default and full-block via MessageBlockLength. Partial because CNG permits any feedback size up to the block, while PKCS#11 defines mechanisms only for 1, 8, 64 and 128 bits; a size with no mechanism is refused rather than silently rounded to a different cipher.</t>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>Nothing, although SoftHSM2 implements fourteen DES mechanisms, so the backend is not the obstacle.</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="inlineStr">
+        <is>
+          <t>Scope and age. Excluded from modern HLK requirements. Implementable at any time; deliberately not implemented.</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="inlineStr">
+        <is>
+          <t>Deliberately out of scope. Deprecated and excluded from modern HLK requirements despite SoftHSM2 supporting 14 DES mechanisms.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>DSA-01</t>
+          <t>AES-08</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Asymmetric DSA</t>
+          <t>Symmetric AES</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>DSA signing</t>
-        </is>
-      </c>
-      <c r="D22" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>AES-CFB</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -7375,31 +7713,46 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>Deliberately out of scope. Deprecated in modern Windows PKI and absent from every HSM KSP surveyed.</t>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>Both feedback sizes CNG can actually reach: the 8-bit default, and full-block through BCRYPT_MESSAGE_BLOCK_LENGTH. CKM_AES_CFB64 is mapped for a MessageBlockLength of 8. All gated on the capability probe and verified against a live token, which asserts the two sizes produce DIFFERENT ciphertext — a provider ignoring the property cannot pass.</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>Two things, and only one of them is ours. The ASYMMETRY is external: CNG permits any feedback size up to the block, PKCS#11 defines mechanisms for four of them, and nothing here can add the missing ones. What is DELIBERATE is the handling — a size with no mechanism is refused rather than rounded to the nearest, because rounding would silently select a different cipher and produce ciphertext nothing else could decrypt. The row is classified as our decision because that refusal is the part a reader might want to argue with.</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>Implemented and verified against a live token for both feedback sizes CNG can reach: the 8-bit default and full-block via MessageBlockLength. Partial because CNG permits any feedback size up to the block, while PKCS#11 defines mechanisms only for 1, 8, 64 and 128 bits; a size with no mechanism is refused rather than silently rounded to a different cipher.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>ECDH-06</t>
+          <t>DSA-01</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Key agreement</t>
+          <t>Asymmetric DSA</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Finite-field Diffie-Hellman</t>
+          <t>DSA signing</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -7412,31 +7765,46 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G23" s="25" t="inlineStr">
-        <is>
-          <t>Out of scope by choice. ECDH supersedes it and no surveyed HSM KSP exposes it. Would need CKM_DH_PKCS_KEY_PAIR_GEN plus CKM_DH_PKCS_DERIVE.</t>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="inlineStr">
+        <is>
+          <t>Scope. Deprecated in modern Windows PKI and absent from every HSM KSP surveyed.</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="inlineStr">
+        <is>
+          <t>Deliberately out of scope. Deprecated in modern Windows PKI and absent from every HSM KSP surveyed.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>FMT-06</t>
+          <t>ECDH-06</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Key formats</t>
+          <t>Key agreement</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Private key export</t>
+          <t>Finite-field Diffie-Hellman</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -7449,21 +7817,36 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>Refused by design with NTE_NOT_SUPPORTED. Keys are CKA_EXTRACTABLE=FALSE. This is correct HSM behaviour not a gap.</t>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>Nothing. ECDH on nine curves covers the agreement surface.</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>Scope. CKM_DH_PKCS_KEY_PAIR_GEN and CKM_DH_PKCS_DERIVE both exist, so this IS implementable — it is excluded because ECDH supersedes it and no surveyed HSM KSP exposes it. Of all the deliberate rows this is the one with the clearest path if a deployment ever needed it.</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>Out of scope by choice. ECDH supersedes it and no surveyed HSM KSP exposes it. Would need CKM_DH_PKCS_KEY_PAIR_GEN plus CKM_DH_PKCS_DERIVE.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>FMT-07</t>
+          <t>FMT-06</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
@@ -7473,7 +7856,7 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Private key import</t>
+          <t>Private key export</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
@@ -7486,21 +7869,36 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G25" s="25" t="inlineStr">
-        <is>
-          <t>Returns NTE_NOT_SUPPORTED. Would need C_CreateObject with private material or C_UnwrapKey. Contradicts the HSM posture; only add if a migration workflow demands it.</t>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>Public key export in CNG blob format for every supported family. Private key export is refused with NTE_NOT_SUPPORTED.</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="inlineStr">
+        <is>
+          <t>The HSM posture, enforced on the token rather than in the provider: keys are CKA_EXTRACTABLE=FALSE unless NCRYPT_EXPORT_POLICY_PROPERTY relaxes it, and even then only wrapped export opens. This is correct behaviour, not an unfinished feature.</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="inlineStr">
+        <is>
+          <t>Refused by design with NTE_NOT_SUPPORTED. Keys are CKA_EXTRACTABLE=FALSE. This is correct HSM behaviour not a gap.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>FMT-09</t>
+          <t>FMT-07</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
@@ -7510,7 +7908,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>PKCS#8 blob</t>
+          <t>Private key import</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -7523,31 +7921,46 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
-        <is>
-          <t>Same constraint as FMT-07: it is a private-key format and keys are non-extractable.</t>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>Public key import creates a real CKO_PUBLIC_KEY; truncated and unknown-curve blobs are rejected rather than silently accepted. Symmetric key unwrap works and creates the key sensitive and non-extractable, so wrapping is a way IN and not a way back out.</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>The HSM posture again. C_CreateObject with private material or C_UnwrapKey would both work, so this is a choice: a key the provider did not generate has an unknown history. Worth revisiting only if a migration workflow demands it.</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>Returns NTE_NOT_SUPPORTED. Would need C_CreateObject with private material or C_UnwrapKey. Contradicts the HSM posture; only add if a migration workflow demands it.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>IFACE-06</t>
+          <t>FMT-09</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Provider interface</t>
+          <t>Key formats</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>GetOperationProperty</t>
+          <t>PKCS#8 blob</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
@@ -7560,14 +7973,29 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G27" s="25" t="inlineStr">
-        <is>
-          <t>Returns NTE_NOT_SUPPORTED. Only needed for overlapped I/O; PKCS#11 is synchronous so there is nothing to report.</t>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>Nothing: it is a private-key format.</t>
+        </is>
+      </c>
+      <c r="I27" s="25" t="inlineStr">
+        <is>
+          <t>FMT-07, exactly. Same posture, same reconsideration trigger.</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="inlineStr">
+        <is>
+          <t>Same constraint as FMT-07: it is a private-key format and keys are non-extractable.</t>
         </is>
       </c>
     </row>
@@ -7597,12 +8025,27 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Refused with NTE_NOT_SUPPORTED.</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>A UI thread and a window handle. A KSP is loaded into whatever process called NCrypt, including services with no desktop, so prompting is a deployment decision rather than a capability to add unconditionally.</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>Returns NTE_NOT_SUPPORTED. Would need a UI thread and a window handle from NCRYPT_WINDOW_HANDLE_PROPERTY.</t>
         </is>
@@ -7634,12 +8077,27 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G29" s="25" t="inlineStr">
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>Refused with NTE_NOT_SUPPORTED.</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="inlineStr">
+        <is>
+          <t>IFACE-07. A UI policy with no prompt to govern would be a stored value nothing reads.</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="inlineStr">
         <is>
           <t>Depends on PromptUser (IFACE-07). Same UI-thread requirement.</t>
         </is>
@@ -7671,12 +8129,27 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>Refused with NTE_NOT_SUPPORTED.</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>IFACE-07, for the same reason as PROP-12.</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>Only meaningful with PromptUser (IFACE-07).</t>
         </is>
@@ -7708,19 +8181,117 @@
           <t>Deliberate position</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>Our choice</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G31" s="25" t="inlineStr">
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>Any multiple of 64 from KSP_RSA_MIN_BITS to 16384. A legacy build can lower the floor; the shipped default refuses below 2048 with NTE_BAD_LEN.</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="inlineStr">
+        <is>
+          <t>A security choice, not a constraint: the mechanism exists and the code path works. Silently allowing 1024 would weaken every deployment that did not ask for it, so it is an opt-in at build time rather than a refusal.</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="inlineStr">
         <is>
           <t>Build-time opt-in only. KSP_RSA_MIN_BITS defaults to 2048; a legacy build can lower it, but the shipped default still rejects &lt;2048 with NTE_BAD_LEN. Deliberate: silently allowing 1024 would weaken every deployment.</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>Gaps outside this matrix’s scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>The matrix tracks capabilities observed across shipping CNG KSPs — the market. A defect in this provider’s OWN conformance surface is not one of those, so no row here would ever point at it. That blind spot has now cost three findings, so they are listed explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>How it was found</t>
+        </is>
+      </c>
+      <c r="D36" s="33" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>NCryptCreatePersistedKey does not return NTE_EXISTS</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Nothing checks whether the name is already taken, so a second create adds a second object with the same CKA_LABEL and NCryptOpenKey returns whichever the token's search hands back first. Microsoft documents NTE_EXISTS for this case, with NCRYPT_OVERWRITE_KEY_FLAG as the way to ask for replacement.</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>While making the two-token suite repeatable: two deletes both reported success and a key was still openable, because earlier runs had left duplicates behind.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Open. Not fixed as part of proposals A to D, because doing it properly means the overwrite flag as well as the check, with tests in both directions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Key-scoped function table slots are unverifiable</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>The mock types every slot as void *, so a wrong parameter TYPE is not a build error on Linux, and MSVC cannot compile ksp_main.c without ncrypt_provider.h. Eight provider-scoped slots are now checked against &lt;ncrypt.h&gt;; key-scoped ones cannot be, because the public prototype is not the slot's shape.</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Session 14, by asking why KSP_NotifyChangeKey had survived with the wrong parameter type.</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Tracked as TABLE-01, which is the one matrix row that does cover a conformance question rather than a capability.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
+  <autoFilter ref="A1:J31"/>
+  <mergeCells count="1">
+    <mergeCell ref="A34:J34"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7746,191 +8317,191 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Implemented and exercised by the test suites. No known gap against the capabilities observed in shipping CNG KSPs.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Implemented and usable with a stated limit: a provider-specific identifier no stock application will ask for, a deliberate refusal, or one working direction of a two-way feature.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Not implemented. Each carries a recorded reason — see "Why still open".</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Evidence grade</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Established inside this repository — read from the source, a header, or proven by a test. The strongest grade and the only one used for this provider's own behaviour.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Vendor documentation or a documentation mirror. Used for what other products do.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Inference from indirect sources. Used sparingly and never for a claim about this provider.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>S / M / L</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Rough size of the remedy IF it were unblocked. It is not a schedule, and a small effort behind a hard blocker is still not startable — TABLE-01 is S and needs a Windows machine.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>No remedy is planned: the row is a deliberate position or an external blocker.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Test layers behind "Yes"</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>22 unit suites, 1816 assertions, Linux/GCC against a controllable PKCS#11 mock. Pins down the provider's logic; cannot validate assumptions about real tokens.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Layer 1b</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>The same provider sources against Kryoptic, an independent PKCS#11 token in Rust. 256 assertions, run twice against one token so anything left behind is caught. Plus 33 concurrency assertions across 32 threads under ThreadSanitizer, and - behind TWO tokens on one module - 53 for token selection and 28 for per-scope isolation, because a single token cannot tell a working selection from an ignored one.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Layer 2 / 3</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Windows integration and HLK-conformant PowerShell suites. Written and syntax-checked; they need a Windows machine with SoftHSM2 to execute.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>What this measures</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>The CNG key-storage surface, as observed across Microsoft Software/Platform Crypto, AWS CloudHSM, Utimaco, Thales, Entrust and Securosys, assessed against this provider.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>What it does not</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Performance, deployment, packaging, and anything about the SoftHSM2 token itself beyond what the provider depends on.</t>
         </is>

--- a/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
+++ b/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CNG Feature Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Category" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Items" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CNG Feature Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="By Category" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Open Items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$104</definedName>
@@ -686,7 +686,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-10-02   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
+          <t>As of 2026-10-07   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8507,6 +8507,25 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>Matrix fingerprint: ffac6b80df68</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>A digest of feature-matrix.csv, coverage_blockers.py, gap_detail.py and this workbook’s generator. tests/check_generated_artifacts.py recomputes it: if the matrix was edited and the workbook was not regenerated, the two disagree and CI fails. Byte-comparing the file itself cannot work — an xlsx is a zip, and neither member order nor timestamps are stable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
+++ b/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CNG Feature Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="By Category" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Open Items" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Legend" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CNG Feature Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Category" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$104</definedName>
@@ -686,7 +686,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-10-07   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
+          <t>As of 2026-10-16   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="34" t="inlineStr">
         <is>
-          <t>Matrix fingerprint: ffac6b80df68</t>
+          <t>Content fingerprint: b9faf9160b28</t>
         </is>
       </c>
       <c r="B27" s="35" t="inlineStr">

--- a/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
+++ b/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Items'!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>As of 2026-10-16   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
+          <t>As of 2026-10-17   ·   source of truth: softhsm_ksp/docs/feature-matrix.csv</t>
         </is>
       </c>
     </row>
@@ -726,8 +726,8 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTA('CNG Feature Matrix'!A2:A104)</f>
-        <v>103</v>
+        <f>COUNTA('CNG Feature Matrix'!A2:A105)</f>
+        <v>104</v>
       </c>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="9" t="inlineStr">
@@ -743,12 +743,12 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"Yes")</f>
-        <v>73</v>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <v>74</v>
       </c>
       <c r="C8" s="12">
         <f>B8/$B$7</f>
-        <v>0.7087378640776699</v>
+        <v>0.7115384615384616</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -763,12 +763,12 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>10</v>
       </c>
       <c r="C9" s="12">
         <f>B9/$B$7</f>
-        <v>0.0970873786407767</v>
+        <v>0.09615384615384616</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -783,12 +783,12 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E105,"No")</f>
         <v>20</v>
       </c>
       <c r="C10" s="12">
         <f>B10/$B$7</f>
-        <v>0.1941747572815534</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A15)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A15)</f>
         <v>11</v>
       </c>
       <c r="C15" s="12">
-        <f>IFERROR(B15/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <f>IFERROR(B15/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
         <v>0.36666666666666664</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -859,11 +859,11 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A16)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A16)</f>
         <v>7</v>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR(B16/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <f>IFERROR(B16/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
         <v>0.23333333333333334</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -879,11 +879,11 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A17)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A17)</f>
         <v>5</v>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR(B17/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <f>IFERROR(B17/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -899,11 +899,11 @@
         </is>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A18)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A18)</f>
         <v>4</v>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(B18/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <f>IFERROR(B18/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
         <v>0.13333333333333333</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -919,11 +919,11 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A19)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A19)</f>
         <v>3</v>
       </c>
       <c r="C19" s="12">
-        <f>IFERROR(B19/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
+        <f>IFERROR(B19/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
         <v>0.1</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -939,12 +939,12 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No"))</f>
+        <f>(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No"))</f>
         <v>30</v>
       </c>
       <c r="C20" s="17">
         <f>IFERROR(B20/$B$7,0)</f>
-        <v>0.2912621359223301</v>
+        <v>0.28846153846153844</v>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5145,22 +5145,22 @@
     <row r="85">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>LIFE-01</t>
+          <t>PROP-19</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>Key lifecycle</t>
+          <t>Key properties</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>CreatePersistedKey</t>
+          <t>NCRYPT_LENGTHS_PROPERTY</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>Immediate and deferred generation</t>
+          <t>Supported key sizes for the algorithm (NCRYPT_SUPPORTED_LENGTHS)</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
@@ -5190,7 +5190,7 @@
     <row r="86">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>LIFE-02</t>
+          <t>LIFE-01</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>FinalizeKey</t>
+          <t>CreatePersistedKey</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Deferred generation trigger</t>
+          <t>Immediate and deferred generation</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
@@ -5235,7 +5235,7 @@
     <row r="87">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>LIFE-03</t>
+          <t>LIFE-02</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="C87" s="24" t="inlineStr">
         <is>
-          <t>OpenKey by name</t>
+          <t>FinalizeKey</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>Asymmetric and symmetric</t>
+          <t>Deferred generation trigger</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
@@ -5280,7 +5280,7 @@
     <row r="88">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>LIFE-04</t>
+          <t>LIFE-03</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>DeleteKey</t>
+          <t>OpenKey by name</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>Destroys all token objects</t>
+          <t>Asymmetric and symmetric</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="89">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>LIFE-05</t>
+          <t>LIFE-04</t>
         </is>
       </c>
       <c r="B89" s="24" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="C89" s="24" t="inlineStr">
         <is>
-          <t>EnumKeys</t>
+          <t>DeleteKey</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>Paged enumeration with state</t>
+          <t>Destroys all token objects</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
@@ -5370,7 +5370,7 @@
     <row r="90">
       <c r="A90" s="21" t="inlineStr">
         <is>
-          <t>LIFE-06</t>
+          <t>LIFE-05</t>
         </is>
       </c>
       <c r="B90" s="21" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>EnumAlgorithms</t>
+          <t>EnumKeys</t>
         </is>
       </c>
       <c r="D90" s="22" t="inlineStr">
         <is>
-          <t>NCryptEnumAlgorithms support</t>
+          <t>Paged enumeration with state</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G90" s="21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H90" s="21" t="inlineStr"/>
@@ -5415,7 +5415,7 @@
     <row r="91">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>LIFE-07</t>
+          <t>LIFE-06</t>
         </is>
       </c>
       <c r="B91" s="24" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="C91" s="24" t="inlineStr">
         <is>
-          <t>IsAlgSupported</t>
+          <t>EnumAlgorithms</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>NCryptIsAlgSupported</t>
+          <t>NCryptEnumAlgorithms support</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
@@ -5460,7 +5460,7 @@
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>LIFE-08</t>
+          <t>LIFE-07</t>
         </is>
       </c>
       <c r="B92" s="21" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>Machine vs user key scope</t>
+          <t>IsAlgSupported</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>NCRYPT_MACHINE_KEY_FLAG is honoured on CreatePersistedKey, OpenKey and EnumKeys. Within one token it is a CKA_LABEL prefix ("m/name" or "u/name"), which keeps distinct keys distinct and is NAMESPACING, NOT ISOLATION. Set KSP_MACHINE_TOKEN_LABEL and KSP_USER_TOKEN_LABEL (or the slot equivalents) and the flag instead selects WHICH TOKEN, each with its own PIN and its own session pool, so isolation is as strong as the token boundary PKCS#11 does have: a caller holding the user PIN cannot read machine keys because it cannot log in to read them. Setting only one of a pair, or two names resolving to one token, is refused rather than half-applied — isolation that reports success and does not isolate is worse than none. Unconfigured behaviour is unchanged. Verified against two real tokens with different PINs, including a case run WITHOUT the machine PIN in which the machine token must be unreachable.</t>
+          <t>NCryptIsAlgSupported</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G92" s="21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H92" s="21" t="inlineStr"/>
@@ -5505,32 +5505,32 @@
     <row r="93">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>LIFE-08</t>
         </is>
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Key lifecycle</t>
         </is>
       </c>
       <c r="C93" s="24" t="inlineStr">
         <is>
-          <t>Hardware key protection</t>
+          <t>Machine vs user key scope</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>Tamper-resistant storage</t>
-        </is>
-      </c>
-      <c r="E93" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>NCRYPT_MACHINE_KEY_FLAG is honoured on CreatePersistedKey, OpenKey and EnumKeys. Within one token it is a CKA_LABEL prefix ("m/name" or "u/name"), which keeps distinct keys distinct and is NAMESPACING, NOT ISOLATION. Set KSP_MACHINE_TOKEN_LABEL and KSP_USER_TOKEN_LABEL (or the slot equivalents) and the flag instead selects WHICH TOKEN, each with its own PIN and its own session pool, so isolation is as strong as the token boundary PKCS#11 does have: a caller holding the user PIN cannot read machine keys because it cannot log in to read them. Setting only one of a pair, or two names resolving to one token, is refused rather than half-applied — isolation that reports success and does not isolate is worse than none. Unconfigured behaviour is unchanged. Verified against two real tokens with different PINs, including a case run WITHOUT the machine PIN in which the machine token must be unreachable.</t>
+        </is>
+      </c>
+      <c r="E93" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F93" s="24" t="inlineStr">
         <is>
-          <t>Not covered</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G93" s="24" t="inlineStr">
@@ -5538,31 +5538,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H93" s="24" t="inlineStr">
-        <is>
-          <t>Blocked: hardware / commercial</t>
-        </is>
-      </c>
-      <c r="I93" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H93" s="24" t="inlineStr"/>
+      <c r="I93" s="24" t="inlineStr"/>
       <c r="J93" s="25" t="inlineStr">
         <is>
-          <t>All commercial providers</t>
-        </is>
-      </c>
-      <c r="K93" s="25" t="inlineStr">
-        <is>
-          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
-        </is>
-      </c>
+          <t>All providers</t>
+        </is>
+      </c>
+      <c r="K93" s="25" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>OPS-02</t>
+          <t>OPS-01</t>
         </is>
       </c>
       <c r="B94" s="21" t="inlineStr">
@@ -5572,12 +5560,12 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>FIPS 140-2/3 validation</t>
+          <t>Hardware key protection</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Certified cryptographic module</t>
+          <t>Tamper-resistant storage</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
@@ -5592,7 +5580,7 @@
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
@@ -5612,14 +5600,14 @@
       </c>
       <c r="K94" s="22" t="inlineStr">
         <is>
-          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
+          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>OPS-02</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
@@ -5629,12 +5617,12 @@
       </c>
       <c r="C95" s="24" t="inlineStr">
         <is>
-          <t>Authenticode-signed binary</t>
+          <t>FIPS 140-2/3 validation</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>Commercial code-signing certificate</t>
+          <t>Certified cryptographic module</t>
         </is>
       </c>
       <c r="E95" s="27" t="inlineStr">
@@ -5649,7 +5637,7 @@
       </c>
       <c r="G95" s="24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H95" s="24" t="inlineStr">
@@ -5669,14 +5657,14 @@
       </c>
       <c r="K95" s="25" t="inlineStr">
         <is>
-          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
+          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>OPS-03</t>
         </is>
       </c>
       <c r="B96" s="21" t="inlineStr">
@@ -5686,42 +5674,54 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Multiple slots / tokens</t>
+          <t>Authenticode-signed binary</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Selecting among several tokens</t>
-        </is>
-      </c>
-      <c r="E96" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Commercial code-signing certificate</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Not covered</t>
         </is>
       </c>
       <c r="G96" s="21" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="inlineStr"/>
-      <c r="I96" s="21" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>Blocked: hardware / commercial</t>
+        </is>
+      </c>
+      <c r="I96" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J96" s="22" t="inlineStr">
         <is>
           <t>All commercial providers</t>
         </is>
       </c>
-      <c r="K96" s="22" t="inlineStr"/>
+      <c r="K96" s="22" t="inlineStr">
+        <is>
+          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>OPS-05</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
@@ -5731,22 +5731,22 @@
       </c>
       <c r="C97" s="24" t="inlineStr">
         <is>
-          <t>Key attestation</t>
+          <t>Multiple slots / tokens</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>TPM / HSM-signed key origin proof</t>
-        </is>
-      </c>
-      <c r="E97" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Selecting among several tokens</t>
+        </is>
+      </c>
+      <c r="E97" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F97" s="24" t="inlineStr">
         <is>
-          <t>Not covered</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G97" s="24" t="inlineStr">
@@ -5754,31 +5754,19 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H97" s="24" t="inlineStr">
-        <is>
-          <t>Blocked: no PKCS#11 mechanism</t>
-        </is>
-      </c>
-      <c r="I97" s="24" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="H97" s="24" t="inlineStr"/>
+      <c r="I97" s="24" t="inlineStr"/>
       <c r="J97" s="25" t="inlineStr">
         <is>
-          <t>MS Platform Crypto; some HSMs</t>
-        </is>
-      </c>
-      <c r="K97" s="25" t="inlineStr">
-        <is>
-          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
-        </is>
-      </c>
+          <t>All commercial providers</t>
+        </is>
+      </c>
+      <c r="K97" s="25" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>OPS-06</t>
+          <t>OPS-05</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
@@ -5788,12 +5776,12 @@
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>Load balancing / HA</t>
+          <t>Key attestation</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Multiple HSM members</t>
+          <t>TPM / HSM-signed key origin proof</t>
         </is>
       </c>
       <c r="E98" s="27" t="inlineStr">
@@ -5808,34 +5796,34 @@
       </c>
       <c r="G98" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
         <is>
-          <t>Blocked: hardware / commercial</t>
+          <t>Blocked: no PKCS#11 mechanism</t>
         </is>
       </c>
       <c r="I98" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="J98" s="22" t="inlineStr">
         <is>
-          <t>Thales; Entrust</t>
+          <t>MS Platform Crypto; some HSMs</t>
         </is>
       </c>
       <c r="K98" s="22" t="inlineStr">
         <is>
-          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
+          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>OPS-07</t>
+          <t>OPS-06</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
@@ -5845,42 +5833,54 @@
       </c>
       <c r="C99" s="24" t="inlineStr">
         <is>
-          <t>Session pool concurrency</t>
+          <t>Load balancing / HA</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>Concurrent NCrypt calls</t>
-        </is>
-      </c>
-      <c r="E99" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Multiple HSM members</t>
+        </is>
+      </c>
+      <c r="E99" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Not covered</t>
         </is>
       </c>
       <c r="G99" s="24" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H99" s="24" t="inlineStr"/>
-      <c r="I99" s="24" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H99" s="24" t="inlineStr">
+        <is>
+          <t>Blocked: hardware / commercial</t>
+        </is>
+      </c>
+      <c r="I99" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J99" s="25" t="inlineStr">
         <is>
-          <t>All providers</t>
-        </is>
-      </c>
-      <c r="K99" s="25" t="inlineStr"/>
+          <t>Thales; Entrust</t>
+        </is>
+      </c>
+      <c r="K99" s="25" t="inlineStr">
+        <is>
+          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>OPS-08</t>
+          <t>OPS-07</t>
         </is>
       </c>
       <c r="B100" s="21" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Re-initialisation without restart</t>
+          <t>Session pool concurrency</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Recover from a bad DLL path</t>
+          <t>Concurrent NCrypt calls</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -5917,7 +5917,7 @@
       <c r="I100" s="21" t="inlineStr"/>
       <c r="J100" s="22" t="inlineStr">
         <is>
-          <t>Vendor-specific</t>
+          <t>All providers</t>
         </is>
       </c>
       <c r="K100" s="22" t="inlineStr"/>
@@ -5925,7 +5925,7 @@
     <row r="101">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>OPS-09</t>
+          <t>OPS-08</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="C101" s="24" t="inlineStr">
         <is>
-          <t>PIN caching / re-login</t>
+          <t>Re-initialisation without restart</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>Session recovery after token logout</t>
+          <t>Recover from a bad DLL path</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -5955,14 +5955,14 @@
       </c>
       <c r="G101" s="24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr"/>
       <c r="I101" s="24" t="inlineStr"/>
       <c r="J101" s="25" t="inlineStr">
         <is>
-          <t>All commercial providers</t>
+          <t>Vendor-specific</t>
         </is>
       </c>
       <c r="K101" s="25" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
     <row r="102">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>OPS-10</t>
+          <t>OPS-09</t>
         </is>
       </c>
       <c r="B102" s="21" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>Logging / diagnostics</t>
+          <t>PIN caching / re-login</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Trace output for support</t>
+          <t>Session recovery after token logout</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
@@ -6000,14 +6000,14 @@
       </c>
       <c r="G102" s="21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H102" s="21" t="inlineStr"/>
       <c r="I102" s="21" t="inlineStr"/>
       <c r="J102" s="22" t="inlineStr">
         <is>
-          <t>All providers</t>
+          <t>All commercial providers</t>
         </is>
       </c>
       <c r="K102" s="22" t="inlineStr"/>
@@ -6015,7 +6015,7 @@
     <row r="103">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>OPS-13</t>
+          <t>OPS-10</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="C103" s="24" t="inlineStr">
         <is>
-          <t>Runtime capability discovery</t>
+          <t>Logging / diagnostics</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>Advertised algorithms reflect what the token implements, not a compiled-in list</t>
+          <t>Trace output for support</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
@@ -6052,7 +6052,7 @@
       <c r="I103" s="24" t="inlineStr"/>
       <c r="J103" s="25" t="inlineStr">
         <is>
-          <t>All commercial providers (implicit — each ships for its own device)</t>
+          <t>All providers</t>
         </is>
       </c>
       <c r="K103" s="25" t="inlineStr"/>
@@ -6060,7 +6060,7 @@
     <row r="104">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>OPS-14</t>
+          <t>OPS-13</t>
         </is>
       </c>
       <c r="B104" s="21" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Backend portability</t>
+          <t>Runtime capability discovery</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Any PKCS#11 v2.40+ module can back the provider (KSP_PKCS11_LIB)</t>
+          <t>Advertised algorithms reflect what the token implements, not a compiled-in list</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -6097,13 +6097,58 @@
       <c r="I104" s="21" t="inlineStr"/>
       <c r="J104" s="22" t="inlineStr">
         <is>
+          <t>All commercial providers (implicit — each ships for its own device)</t>
+        </is>
+      </c>
+      <c r="K104" s="22" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="24" t="inlineStr">
+        <is>
+          <t>OPS-14</t>
+        </is>
+      </c>
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="inlineStr">
+        <is>
+          <t>Backend portability</t>
+        </is>
+      </c>
+      <c r="D105" s="25" t="inlineStr">
+        <is>
+          <t>Any PKCS#11 v2.40+ module can back the provider (KSP_PKCS11_LIB)</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" s="24" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="G105" s="24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H105" s="24" t="inlineStr"/>
+      <c r="I105" s="24" t="inlineStr"/>
+      <c r="J105" s="25" t="inlineStr">
+        <is>
           <t>Not offered — commercial providers are bound to their own hardware</t>
         </is>
       </c>
-      <c r="K104" s="22" t="inlineStr"/>
+      <c r="K105" s="25" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K104"/>
+  <autoFilter ref="A1:K105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6171,15 +6216,15 @@
         </is>
       </c>
       <c r="B4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A4,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A4,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A4,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>1</v>
       </c>
       <c r="E4" s="15">
@@ -6198,15 +6243,15 @@
         </is>
       </c>
       <c r="B5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A5,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>6</v>
       </c>
       <c r="C5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A5,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A5,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>0</v>
       </c>
       <c r="E5" s="15">
@@ -6225,15 +6270,15 @@
         </is>
       </c>
       <c r="B6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A6,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>1</v>
       </c>
       <c r="C6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A6,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>2</v>
       </c>
       <c r="D6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A6,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>0</v>
       </c>
       <c r="E6" s="15">
@@ -6252,15 +6297,15 @@
         </is>
       </c>
       <c r="B7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A7,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>11</v>
       </c>
       <c r="C7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A7,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A7,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>0</v>
       </c>
       <c r="E7" s="15">
@@ -6279,15 +6324,15 @@
         </is>
       </c>
       <c r="B8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A8,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>5</v>
       </c>
       <c r="C8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A8,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A8,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>1</v>
       </c>
       <c r="E8" s="15">
@@ -6306,15 +6351,15 @@
         </is>
       </c>
       <c r="B9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A9,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>6</v>
       </c>
       <c r="C9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A9,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A9,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>4</v>
       </c>
       <c r="E9" s="15">
@@ -6333,15 +6378,15 @@
         </is>
       </c>
       <c r="B10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A10,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>8</v>
       </c>
       <c r="C10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A10,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A10,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>0</v>
       </c>
       <c r="E10" s="15">
@@ -6360,24 +6405,24 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"Yes")</f>
-        <v>13</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A11,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <v>14</v>
       </c>
       <c r="C11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A11,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A11,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>4</v>
       </c>
       <c r="E11" s="15">
         <f>SUM(B11:D11)</f>
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="F11" s="12">
         <f>IFERROR(B11/E11,0)</f>
-        <v>0.7647058823529411</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -6387,15 +6432,15 @@
         </is>
       </c>
       <c r="B12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A12,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>7</v>
       </c>
       <c r="C12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A12,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A12,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>5</v>
       </c>
       <c r="E12" s="15">
@@ -6414,15 +6459,15 @@
         </is>
       </c>
       <c r="B13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A13,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A13,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A13,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>2</v>
       </c>
       <c r="E13" s="15">
@@ -6441,15 +6486,15 @@
         </is>
       </c>
       <c r="B14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A14,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>7</v>
       </c>
       <c r="C14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A14,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>3</v>
       </c>
       <c r="D14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A14,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>2</v>
       </c>
       <c r="E14" s="15">
@@ -6468,15 +6513,15 @@
         </is>
       </c>
       <c r="B15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A15,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>8</v>
       </c>
       <c r="C15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A15,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>2</v>
       </c>
       <c r="D15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A15,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>0</v>
       </c>
       <c r="E15" s="15">
@@ -6495,15 +6540,15 @@
         </is>
       </c>
       <c r="B16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A16,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>1</v>
       </c>
       <c r="C16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A16,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A16,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>0</v>
       </c>
       <c r="E16" s="15">
@@ -6522,15 +6567,15 @@
         </is>
       </c>
       <c r="B17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A17,'CNG Feature Matrix'!E2:E105,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A17,'CNG Feature Matrix'!E2:E105,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A17,'CNG Feature Matrix'!E2:E105,"No")</f>
         <v>1</v>
       </c>
       <c r="E17" s="15">
@@ -6550,7 +6595,7 @@
       </c>
       <c r="B18" s="7">
         <f>SUM(B4:B17)</f>
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="C18" s="7">
         <f>SUM(C4:C17)</f>
@@ -6562,11 +6607,11 @@
       </c>
       <c r="E18" s="7">
         <f>SUM(E4:E17)</f>
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="F18" s="17">
         <f>IFERROR(B18/E18,0)</f>
-        <v>0.7087378640776699</v>
+        <v>0.7115384615384616</v>
       </c>
     </row>
   </sheetData>
@@ -8517,7 +8562,7 @@
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="34" t="inlineStr">
         <is>
-          <t>Content fingerprint: b9faf9160b28</t>
+          <t>Content fingerprint: 29efcc6709fa</t>
         </is>
       </c>
       <c r="B27" s="35" t="inlineStr">

--- a/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
+++ b/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
@@ -6625,7 +6625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8291,42 +8291,20 @@
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>NCryptCreatePersistedKey does not return NTE_EXISTS</t>
+          <t>Key-scoped function table slots are unverifiable</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Nothing checks whether the name is already taken, so a second create adds a second object with the same CKA_LABEL and NCryptOpenKey returns whichever the token's search hands back first. Microsoft documents NTE_EXISTS for this case, with NCRYPT_OVERWRITE_KEY_FLAG as the way to ask for replacement.</t>
+          <t>The mock types every slot as void *, so a wrong parameter TYPE is not a build error on Linux, and MSVC cannot compile ksp_main.c without ncrypt_provider.h. Eight provider-scoped slots are now checked against &lt;ncrypt.h&gt;; key-scoped ones cannot be, because the public prototype is not the slot's shape.</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>While making the two-token suite repeatable: two deletes both reported success and a key was still openable, because earlier runs had left duplicates behind.</t>
+          <t>Session 14, by asking why KSP_NotifyChangeKey had survived with the wrong parameter type.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Open. Not fixed as part of proposals A to D, because doing it properly means the overwrite flag as well as the check, with tests in both directions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Key-scoped function table slots are unverifiable</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>The mock types every slot as void *, so a wrong parameter TYPE is not a build error on Linux, and MSVC cannot compile ksp_main.c without ncrypt_provider.h. Eight provider-scoped slots are now checked against &lt;ncrypt.h&gt;; key-scoped ones cannot be, because the public prototype is not the slot's shape.</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Session 14, by asking why KSP_NotifyChangeKey had survived with the wrong parameter type.</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Tracked as TABLE-01, which is the one matrix row that does cover a conformance question rather than a capability.</t>
         </is>
@@ -8562,7 +8540,7 @@
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="34" t="inlineStr">
         <is>
-          <t>Content fingerprint: 29efcc6709fa</t>
+          <t>Content fingerprint: 95ac57998880</t>
         </is>
       </c>
       <c r="B27" s="35" t="inlineStr">

--- a/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
+++ b/softhsm_ksp/SoftHSM2_KSP_CNG_Feature_Coverage.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CNG Feature Matrix'!$A$1:$K$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Items'!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -726,8 +726,8 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTA('CNG Feature Matrix'!A2:A105)</f>
-        <v>104</v>
+        <f>COUNTA('CNG Feature Matrix'!A2:A104)</f>
+        <v>103</v>
       </c>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="9" t="inlineStr">
@@ -743,12 +743,12 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E105,"Yes")</f>
-        <v>74</v>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>73</v>
       </c>
       <c r="C8" s="12">
         <f>B8/$B$7</f>
-        <v>0.7115384615384616</v>
+        <v>0.7087378640776699</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -763,12 +763,12 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>10</v>
       </c>
       <c r="C9" s="12">
         <f>B9/$B$7</f>
-        <v>0.09615384615384616</v>
+        <v>0.0970873786407767</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -783,12 +783,12 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTIF('CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIF('CNG Feature Matrix'!E2:E104,"No")</f>
         <v>20</v>
       </c>
       <c r="C10" s="12">
         <f>B10/$B$7</f>
-        <v>0.19230769230769232</v>
+        <v>0.1941747572815534</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A15)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A15)</f>
         <v>11</v>
       </c>
       <c r="C15" s="12">
-        <f>IFERROR(B15/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
+        <f>IFERROR(B15/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
         <v>0.36666666666666664</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -859,11 +859,11 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A16)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A16)</f>
         <v>7</v>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR(B16/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
+        <f>IFERROR(B16/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
         <v>0.23333333333333334</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -879,11 +879,11 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A17)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A17)</f>
         <v>5</v>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR(B17/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
+        <f>IFERROR(B17/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -899,11 +899,11 @@
         </is>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A18)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A18)</f>
         <v>4</v>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(B18/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
+        <f>IFERROR(B18/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
         <v>0.13333333333333333</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -919,11 +919,11 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF('CNG Feature Matrix'!H2:H105,A19)</f>
+        <f>COUNTIF('CNG Feature Matrix'!H2:H104,A19)</f>
         <v>3</v>
       </c>
       <c r="C19" s="12">
-        <f>IFERROR(B19/(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No")),0)</f>
+        <f>IFERROR(B19/(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No")),0)</f>
         <v>0.1</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -939,12 +939,12 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>(COUNTIF('CNG Feature Matrix'!E2:E105,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E105,"No"))</f>
+        <f>(COUNTIF('CNG Feature Matrix'!E2:E104,"Partial")+COUNTIF('CNG Feature Matrix'!E2:E104,"No"))</f>
         <v>30</v>
       </c>
       <c r="C20" s="17">
         <f>IFERROR(B20/$B$7,0)</f>
-        <v>0.28846153846153844</v>
+        <v>0.2912621359223301</v>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Always 0 (non-exportable)</t>
+          <t>Caller declares before FinalizeKey whether a key may leave the token and in what form; default 0 seals it</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>PROP-18</t>
+          <t>PROP-19</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>NCRYPT_EXPORT_POLICY_PROPERTY</t>
+          <t>NCRYPT_LENGTHS_PROPERTY</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Caller declares at creation whether a key may leave the token</t>
+          <t>Supported key sizes for the algorithm (NCRYPT_SUPPORTED_LENGTHS)</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
@@ -5137,7 +5137,7 @@
       <c r="I84" s="21" t="inlineStr"/>
       <c r="J84" s="22" t="inlineStr">
         <is>
-          <t>MS Software KSP; every provider that supports key backup</t>
+          <t>All providers</t>
         </is>
       </c>
       <c r="K84" s="22" t="inlineStr"/>
@@ -5145,22 +5145,22 @@
     <row r="85">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>PROP-19</t>
+          <t>LIFE-01</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>Key properties</t>
+          <t>Key lifecycle</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>NCRYPT_LENGTHS_PROPERTY</t>
+          <t>CreatePersistedKey</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>Supported key sizes for the algorithm (NCRYPT_SUPPORTED_LENGTHS)</t>
+          <t>Immediate and deferred generation</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
@@ -5190,7 +5190,7 @@
     <row r="86">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>LIFE-01</t>
+          <t>LIFE-02</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>CreatePersistedKey</t>
+          <t>FinalizeKey</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Immediate and deferred generation</t>
+          <t>Deferred generation trigger</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
@@ -5235,7 +5235,7 @@
     <row r="87">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>LIFE-02</t>
+          <t>LIFE-03</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="C87" s="24" t="inlineStr">
         <is>
-          <t>FinalizeKey</t>
+          <t>OpenKey by name</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>Deferred generation trigger</t>
+          <t>Asymmetric and symmetric</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
@@ -5280,7 +5280,7 @@
     <row r="88">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>LIFE-03</t>
+          <t>LIFE-04</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>OpenKey by name</t>
+          <t>DeleteKey</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>Asymmetric and symmetric</t>
+          <t>Destroys all token objects</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="89">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>LIFE-04</t>
+          <t>LIFE-05</t>
         </is>
       </c>
       <c r="B89" s="24" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="C89" s="24" t="inlineStr">
         <is>
-          <t>DeleteKey</t>
+          <t>EnumKeys</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>Destroys all token objects</t>
+          <t>Paged enumeration with state</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
@@ -5370,7 +5370,7 @@
     <row r="90">
       <c r="A90" s="21" t="inlineStr">
         <is>
-          <t>LIFE-05</t>
+          <t>LIFE-06</t>
         </is>
       </c>
       <c r="B90" s="21" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>EnumKeys</t>
+          <t>EnumAlgorithms</t>
         </is>
       </c>
       <c r="D90" s="22" t="inlineStr">
         <is>
-          <t>Paged enumeration with state</t>
+          <t>NCryptEnumAlgorithms support</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G90" s="21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H90" s="21" t="inlineStr"/>
@@ -5415,7 +5415,7 @@
     <row r="91">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>LIFE-06</t>
+          <t>LIFE-07</t>
         </is>
       </c>
       <c r="B91" s="24" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="C91" s="24" t="inlineStr">
         <is>
-          <t>EnumAlgorithms</t>
+          <t>IsAlgSupported</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>NCryptEnumAlgorithms support</t>
+          <t>NCryptIsAlgSupported</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
@@ -5460,7 +5460,7 @@
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>LIFE-07</t>
+          <t>LIFE-08</t>
         </is>
       </c>
       <c r="B92" s="21" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>IsAlgSupported</t>
+          <t>Machine vs user key scope</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>NCryptIsAlgSupported</t>
+          <t>NCRYPT_MACHINE_KEY_FLAG is honoured on CreatePersistedKey, OpenKey and EnumKeys. Within one token it is a CKA_LABEL prefix ("m/name" or "u/name"), which keeps distinct keys distinct and is NAMESPACING, NOT ISOLATION. Set KSP_MACHINE_TOKEN_LABEL and KSP_USER_TOKEN_LABEL (or the slot equivalents) and the flag instead selects WHICH TOKEN, each with its own PIN and its own session pool, so isolation is as strong as the token boundary PKCS#11 does have: a caller holding the user PIN cannot read machine keys because it cannot log in to read them. Setting only one of a pair, or two names resolving to one token, is refused rather than half-applied — isolation that reports success and does not isolate is worse than none. Unconfigured behaviour is unchanged. Verified against two real tokens with different PINs, including a case run WITHOUT the machine PIN in which the machine token must be unreachable.</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G92" s="21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H92" s="21" t="inlineStr"/>
@@ -5505,32 +5505,32 @@
     <row r="93">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>LIFE-08</t>
+          <t>OPS-01</t>
         </is>
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>Key lifecycle</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C93" s="24" t="inlineStr">
         <is>
-          <t>Machine vs user key scope</t>
+          <t>Hardware key protection</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>NCRYPT_MACHINE_KEY_FLAG is honoured on CreatePersistedKey, OpenKey and EnumKeys. Within one token it is a CKA_LABEL prefix ("m/name" or "u/name"), which keeps distinct keys distinct and is NAMESPACING, NOT ISOLATION. Set KSP_MACHINE_TOKEN_LABEL and KSP_USER_TOKEN_LABEL (or the slot equivalents) and the flag instead selects WHICH TOKEN, each with its own PIN and its own session pool, so isolation is as strong as the token boundary PKCS#11 does have: a caller holding the user PIN cannot read machine keys because it cannot log in to read them. Setting only one of a pair, or two names resolving to one token, is refused rather than half-applied — isolation that reports success and does not isolate is worse than none. Unconfigured behaviour is unchanged. Verified against two real tokens with different PINs, including a case run WITHOUT the machine PIN in which the machine token must be unreachable.</t>
-        </is>
-      </c>
-      <c r="E93" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Tamper-resistant storage</t>
+        </is>
+      </c>
+      <c r="E93" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F93" s="24" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Not covered</t>
         </is>
       </c>
       <c r="G93" s="24" t="inlineStr">
@@ -5538,19 +5538,31 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H93" s="24" t="inlineStr"/>
-      <c r="I93" s="24" t="inlineStr"/>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>Blocked: hardware / commercial</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J93" s="25" t="inlineStr">
         <is>
-          <t>All providers</t>
-        </is>
-      </c>
-      <c r="K93" s="25" t="inlineStr"/>
+          <t>All commercial providers</t>
+        </is>
+      </c>
+      <c r="K93" s="25" t="inlineStr">
+        <is>
+          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>OPS-02</t>
         </is>
       </c>
       <c r="B94" s="21" t="inlineStr">
@@ -5560,12 +5572,12 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Hardware key protection</t>
+          <t>FIPS 140-2/3 validation</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Tamper-resistant storage</t>
+          <t>Certified cryptographic module</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
@@ -5580,7 +5592,7 @@
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
@@ -5600,14 +5612,14 @@
       </c>
       <c r="K94" s="22" t="inlineStr">
         <is>
-          <t>Fundamental: SoftHSM2 is a software token using encrypted SQLite. Only fixable by pointing the KSP at a real HSM which the PKCS#11 abstraction already allows.</t>
+          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>OPS-02</t>
+          <t>OPS-03</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
@@ -5617,12 +5629,12 @@
       </c>
       <c r="C95" s="24" t="inlineStr">
         <is>
-          <t>FIPS 140-2/3 validation</t>
+          <t>Authenticode-signed binary</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>Certified cryptographic module</t>
+          <t>Commercial code-signing certificate</t>
         </is>
       </c>
       <c r="E95" s="27" t="inlineStr">
@@ -5637,7 +5649,7 @@
       </c>
       <c r="G95" s="24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H95" s="24" t="inlineStr">
@@ -5657,14 +5669,14 @@
       </c>
       <c r="K95" s="25" t="inlineStr">
         <is>
-          <t>Follows from OPS-01. Requires certified hardware and a formal validation programme.</t>
+          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="B96" s="21" t="inlineStr">
@@ -5674,54 +5686,42 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Authenticode-signed binary</t>
+          <t>Multiple slots / tokens</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Commercial code-signing certificate</t>
-        </is>
-      </c>
-      <c r="E96" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Selecting among several tokens</t>
+        </is>
+      </c>
+      <c r="E96" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>Not covered</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G96" s="21" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="inlineStr">
-        <is>
-          <t>Blocked: hardware / commercial</t>
-        </is>
-      </c>
-      <c r="I96" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr"/>
+      <c r="I96" s="21" t="inlineStr"/>
       <c r="J96" s="22" t="inlineStr">
         <is>
           <t>All commercial providers</t>
         </is>
       </c>
-      <c r="K96" s="22" t="inlineStr">
-        <is>
-          <t>Signing is fully tooled: tools/sign_ksp.ps1 signs, timestamps and verifies, taking a certificate from the Windows store, a PFX (password from the environment, never a parameter) or Azure Trusted Signing, and the CI windows job signs automatically once the KSP_SIGN_PFX_BASE64 secret exists. What remains is not engineering: an OV or EV code-signing certificate must be bought by a verified legal entity. Nothing in this repository can supply that, so the row stays Not covered — the binary is unsigned.</t>
-        </is>
-      </c>
+      <c r="K96" s="22" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>OPS-05</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
@@ -5731,22 +5731,22 @@
       </c>
       <c r="C97" s="24" t="inlineStr">
         <is>
-          <t>Multiple slots / tokens</t>
+          <t>Key attestation</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>Selecting among several tokens</t>
-        </is>
-      </c>
-      <c r="E97" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>TPM / HSM-signed key origin proof</t>
+        </is>
+      </c>
+      <c r="E97" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F97" s="24" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Not covered</t>
         </is>
       </c>
       <c r="G97" s="24" t="inlineStr">
@@ -5754,19 +5754,31 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H97" s="24" t="inlineStr"/>
-      <c r="I97" s="24" t="inlineStr"/>
+      <c r="H97" s="24" t="inlineStr">
+        <is>
+          <t>Blocked: no PKCS#11 mechanism</t>
+        </is>
+      </c>
+      <c r="I97" s="24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="J97" s="25" t="inlineStr">
         <is>
-          <t>All commercial providers</t>
-        </is>
-      </c>
-      <c r="K97" s="25" t="inlineStr"/>
+          <t>MS Platform Crypto; some HSMs</t>
+        </is>
+      </c>
+      <c r="K97" s="25" t="inlineStr">
+        <is>
+          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>OPS-05</t>
+          <t>OPS-06</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
@@ -5776,12 +5788,12 @@
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>Key attestation</t>
+          <t>Load balancing / HA</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>TPM / HSM-signed key origin proof</t>
+          <t>Multiple HSM members</t>
         </is>
       </c>
       <c r="E98" s="27" t="inlineStr">
@@ -5796,34 +5808,34 @@
       </c>
       <c r="G98" s="21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
         <is>
-          <t>Blocked: no PKCS#11 mechanism</t>
+          <t>Blocked: hardware / commercial</t>
         </is>
       </c>
       <c r="I98" s="21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J98" s="22" t="inlineStr">
         <is>
-          <t>MS Platform Crypto; some HSMs</t>
+          <t>Thales; Entrust</t>
         </is>
       </c>
       <c r="K98" s="22" t="inlineStr">
         <is>
-          <t>No PKCS#11 standard mechanism exists. Vendor-specific and unreachable through a portable PKCS#11 layer.</t>
+          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>OPS-06</t>
+          <t>OPS-07</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
@@ -5833,54 +5845,42 @@
       </c>
       <c r="C99" s="24" t="inlineStr">
         <is>
-          <t>Load balancing / HA</t>
+          <t>Session pool concurrency</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>Multiple HSM members</t>
-        </is>
-      </c>
-      <c r="E99" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Concurrent NCrypt calls</t>
+        </is>
+      </c>
+      <c r="E99" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
-          <t>Not covered</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="G99" s="24" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H99" s="24" t="inlineStr">
-        <is>
-          <t>Blocked: hardware / commercial</t>
-        </is>
-      </c>
-      <c r="I99" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H99" s="24" t="inlineStr"/>
+      <c r="I99" s="24" t="inlineStr"/>
       <c r="J99" s="25" t="inlineStr">
         <is>
-          <t>Thales; Entrust</t>
-        </is>
-      </c>
-      <c r="K99" s="25" t="inlineStr">
-        <is>
-          <t>Handled inside vendor PKCS#11 libraries. Our KSP would inherit it automatically when pointed at such a library; nothing to implement.</t>
-        </is>
-      </c>
+          <t>All providers</t>
+        </is>
+      </c>
+      <c r="K99" s="25" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>OPS-07</t>
+          <t>OPS-08</t>
         </is>
       </c>
       <c r="B100" s="21" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Session pool concurrency</t>
+          <t>Re-initialisation without restart</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Concurrent NCrypt calls</t>
+          <t>Recover from a bad DLL path</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -5917,7 +5917,7 @@
       <c r="I100" s="21" t="inlineStr"/>
       <c r="J100" s="22" t="inlineStr">
         <is>
-          <t>All providers</t>
+          <t>Vendor-specific</t>
         </is>
       </c>
       <c r="K100" s="22" t="inlineStr"/>
@@ -5925,7 +5925,7 @@
     <row r="101">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>OPS-08</t>
+          <t>OPS-09</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="C101" s="24" t="inlineStr">
         <is>
-          <t>Re-initialisation without restart</t>
+          <t>PIN caching / re-login</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>Recover from a bad DLL path</t>
+          <t>Session recovery after token logout</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -5955,14 +5955,14 @@
       </c>
       <c r="G101" s="24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr"/>
       <c r="I101" s="24" t="inlineStr"/>
       <c r="J101" s="25" t="inlineStr">
         <is>
-          <t>Vendor-specific</t>
+          <t>All commercial providers</t>
         </is>
       </c>
       <c r="K101" s="25" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
     <row r="102">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>OPS-09</t>
+          <t>OPS-10</t>
         </is>
       </c>
       <c r="B102" s="21" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>PIN caching / re-login</t>
+          <t>Logging / diagnostics</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Session recovery after token logout</t>
+          <t>Trace output for support</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
@@ -6000,14 +6000,14 @@
       </c>
       <c r="G102" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H102" s="21" t="inlineStr"/>
       <c r="I102" s="21" t="inlineStr"/>
       <c r="J102" s="22" t="inlineStr">
         <is>
-          <t>All commercial providers</t>
+          <t>All providers</t>
         </is>
       </c>
       <c r="K102" s="22" t="inlineStr"/>
@@ -6015,7 +6015,7 @@
     <row r="103">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>OPS-10</t>
+          <t>OPS-13</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="C103" s="24" t="inlineStr">
         <is>
-          <t>Logging / diagnostics</t>
+          <t>Runtime capability discovery</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>Trace output for support</t>
+          <t>Advertised algorithms reflect what the token implements, not a compiled-in list</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
@@ -6052,7 +6052,7 @@
       <c r="I103" s="24" t="inlineStr"/>
       <c r="J103" s="25" t="inlineStr">
         <is>
-          <t>All providers</t>
+          <t>All commercial providers (implicit — each ships for its own device)</t>
         </is>
       </c>
       <c r="K103" s="25" t="inlineStr"/>
@@ -6060,7 +6060,7 @@
     <row r="104">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>OPS-13</t>
+          <t>OPS-14</t>
         </is>
       </c>
       <c r="B104" s="21" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Runtime capability discovery</t>
+          <t>Backend portability</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Advertised algorithms reflect what the token implements, not a compiled-in list</t>
+          <t>Any PKCS#11 v2.40+ module can back the provider (KSP_PKCS11_LIB)</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -6097,58 +6097,13 @@
       <c r="I104" s="21" t="inlineStr"/>
       <c r="J104" s="22" t="inlineStr">
         <is>
-          <t>All commercial providers (implicit — each ships for its own device)</t>
+          <t>Not offered — commercial providers are bound to their own hardware</t>
         </is>
       </c>
       <c r="K104" s="22" t="inlineStr"/>
     </row>
-    <row r="105">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>OPS-14</t>
-        </is>
-      </c>
-      <c r="B105" s="24" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="C105" s="24" t="inlineStr">
-        <is>
-          <t>Backend portability</t>
-        </is>
-      </c>
-      <c r="D105" s="25" t="inlineStr">
-        <is>
-          <t>Any PKCS#11 v2.40+ module can back the provider (KSP_PKCS11_LIB)</t>
-        </is>
-      </c>
-      <c r="E105" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F105" s="24" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-      <c r="G105" s="24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H105" s="24" t="inlineStr"/>
-      <c r="I105" s="24" t="inlineStr"/>
-      <c r="J105" s="25" t="inlineStr">
-        <is>
-          <t>Not offered — commercial providers are bound to their own hardware</t>
-        </is>
-      </c>
-      <c r="K105" s="25" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K105"/>
+  <autoFilter ref="A1:K104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6216,15 +6171,15 @@
         </is>
       </c>
       <c r="B4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A4,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A4,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D4" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A4,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A4,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>1</v>
       </c>
       <c r="E4" s="15">
@@ -6243,15 +6198,15 @@
         </is>
       </c>
       <c r="B5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A5,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>6</v>
       </c>
       <c r="C5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A5,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D5" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A5,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A5,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E5" s="15">
@@ -6270,15 +6225,15 @@
         </is>
       </c>
       <c r="B6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A6,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>1</v>
       </c>
       <c r="C6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A6,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>2</v>
       </c>
       <c r="D6" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A6,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A6,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E6" s="15">
@@ -6297,15 +6252,15 @@
         </is>
       </c>
       <c r="B7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A7,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>11</v>
       </c>
       <c r="C7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A7,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D7" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A7,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A7,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E7" s="15">
@@ -6324,15 +6279,15 @@
         </is>
       </c>
       <c r="B8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A8,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>5</v>
       </c>
       <c r="C8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A8,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D8" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A8,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A8,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>1</v>
       </c>
       <c r="E8" s="15">
@@ -6351,15 +6306,15 @@
         </is>
       </c>
       <c r="B9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A9,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>6</v>
       </c>
       <c r="C9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A9,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D9" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A9,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A9,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>4</v>
       </c>
       <c r="E9" s="15">
@@ -6378,15 +6333,15 @@
         </is>
       </c>
       <c r="B10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A10,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>8</v>
       </c>
       <c r="C10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A10,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D10" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A10,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A10,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E10" s="15">
@@ -6405,24 +6360,24 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A11,'CNG Feature Matrix'!E2:E105,"Yes")</f>
-        <v>14</v>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"Yes")</f>
+        <v>13</v>
       </c>
       <c r="C11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A11,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D11" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A11,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A11,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>4</v>
       </c>
       <c r="E11" s="15">
         <f>SUM(B11:D11)</f>
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="F11" s="12">
         <f>IFERROR(B11/E11,0)</f>
-        <v>0.7777777777777778</v>
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="12">
@@ -6432,15 +6387,15 @@
         </is>
       </c>
       <c r="B12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A12,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>7</v>
       </c>
       <c r="C12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A12,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D12" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A12,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A12,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>5</v>
       </c>
       <c r="E12" s="15">
@@ -6459,15 +6414,15 @@
         </is>
       </c>
       <c r="B13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A13,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A13,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D13" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A13,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A13,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>2</v>
       </c>
       <c r="E13" s="15">
@@ -6486,15 +6441,15 @@
         </is>
       </c>
       <c r="B14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A14,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>7</v>
       </c>
       <c r="C14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A14,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>3</v>
       </c>
       <c r="D14" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A14,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A14,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>2</v>
       </c>
       <c r="E14" s="15">
@@ -6513,15 +6468,15 @@
         </is>
       </c>
       <c r="B15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A15,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>8</v>
       </c>
       <c r="C15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A15,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>2</v>
       </c>
       <c r="D15" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A15,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A15,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E15" s="15">
@@ -6540,15 +6495,15 @@
         </is>
       </c>
       <c r="B16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A16,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>1</v>
       </c>
       <c r="C16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A16,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D16" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A16,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A16,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>0</v>
       </c>
       <c r="E16" s="15">
@@ -6567,15 +6522,15 @@
         </is>
       </c>
       <c r="B17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A17,'CNG Feature Matrix'!E2:E105,"Yes")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A17,'CNG Feature Matrix'!E2:E105,"Partial")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D17" s="29">
-        <f>COUNTIFS('CNG Feature Matrix'!B2:B105,$A17,'CNG Feature Matrix'!E2:E105,"No")</f>
+        <f>COUNTIFS('CNG Feature Matrix'!B2:B104,$A17,'CNG Feature Matrix'!E2:E104,"No")</f>
         <v>1</v>
       </c>
       <c r="E17" s="15">
@@ -6595,7 +6550,7 @@
       </c>
       <c r="B18" s="7">
         <f>SUM(B4:B17)</f>
-        <v>74.0</v>
+        <v>73.0</v>
       </c>
       <c r="C18" s="7">
         <f>SUM(C4:C17)</f>
@@ -6607,11 +6562,11 @@
       </c>
       <c r="E18" s="7">
         <f>SUM(E4:E17)</f>
-        <v>104.0</v>
+        <v>103.0</v>
       </c>
       <c r="F18" s="17">
         <f>IFERROR(B18/E18,0)</f>
-        <v>0.7115384615384616</v>
+        <v>0.7087378640776699</v>
       </c>
     </row>
   </sheetData>
@@ -8540,7 +8495,7 @@
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="34" t="inlineStr">
         <is>
-          <t>Content fingerprint: 95ac57998880</t>
+          <t>Content fingerprint: 6ae4217b85c8</t>
         </is>
       </c>
       <c r="B27" s="35" t="inlineStr">
